--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -10412,10 +10412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121175096</v>
+        <v>121173075</v>
       </c>
       <c r="B87" t="n">
-        <v>98071</v>
+        <v>79679</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10424,50 +10424,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor -Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491249</v>
+        <v>491094</v>
       </c>
       <c r="R87" t="n">
-        <v>6943270</v>
+        <v>6943719</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10527,7 +10518,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121173101</v>
+        <v>121175096</v>
       </c>
       <c r="B88" t="n">
         <v>98071</v>
@@ -10575,14 +10566,14 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor -Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491378</v>
+        <v>491249</v>
       </c>
       <c r="R88" t="n">
-        <v>6943184</v>
+        <v>6943270</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10642,10 +10633,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121173075</v>
+        <v>121173101</v>
       </c>
       <c r="B89" t="n">
-        <v>79679</v>
+        <v>98071</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10654,30 +10645,39 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10685,10 +10685,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491094</v>
+        <v>491378</v>
       </c>
       <c r="R89" t="n">
-        <v>6943719</v>
+        <v>6943184</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -10078,7 +10078,7 @@
         <v>120846313</v>
       </c>
       <c r="B84" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120846304</v>
+        <v>120846326</v>
       </c>
       <c r="B85" t="n">
-        <v>98071</v>
+        <v>97035</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10202,37 +10202,29 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
@@ -10242,10 +10234,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>491215</v>
+        <v>491199</v>
       </c>
       <c r="R85" t="n">
-        <v>6943317</v>
+        <v>6943383</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10305,10 +10297,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120846326</v>
+        <v>120846304</v>
       </c>
       <c r="B86" t="n">
-        <v>97025</v>
+        <v>98081</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10317,29 +10309,37 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
@@ -10349,10 +10349,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491199</v>
+        <v>491215</v>
       </c>
       <c r="R86" t="n">
-        <v>6943383</v>
+        <v>6943317</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10412,10 +10412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121173075</v>
+        <v>121174716</v>
       </c>
       <c r="B87" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10424,30 +10424,39 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10455,10 +10464,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491094</v>
+        <v>491104</v>
       </c>
       <c r="R87" t="n">
-        <v>6943719</v>
+        <v>6943581</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10518,10 +10527,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121175096</v>
+        <v>121174642</v>
       </c>
       <c r="B88" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10553,7 +10562,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10566,14 +10575,14 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor -Öravattnet, Jmt</t>
+          <t>Stor-lravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491249</v>
+        <v>491319</v>
       </c>
       <c r="R88" t="n">
-        <v>6943270</v>
+        <v>6943212</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10633,10 +10642,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121173101</v>
+        <v>121172997</v>
       </c>
       <c r="B89" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10645,39 +10654,30 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10685,10 +10685,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491378</v>
+        <v>491043</v>
       </c>
       <c r="R89" t="n">
-        <v>6943184</v>
+        <v>6943791</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10721,6 +10721,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10748,10 +10753,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121174736</v>
+        <v>121173030</v>
       </c>
       <c r="B90" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10760,39 +10765,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10800,10 +10796,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491093</v>
+        <v>491061</v>
       </c>
       <c r="R90" t="n">
-        <v>6943580</v>
+        <v>6943779</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10863,10 +10859,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121173058</v>
+        <v>121173054</v>
       </c>
       <c r="B91" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10906,10 +10902,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491060</v>
+        <v>491077</v>
       </c>
       <c r="R91" t="n">
-        <v>6943711</v>
+        <v>6943749</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10969,10 +10965,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121173066</v>
+        <v>121174736</v>
       </c>
       <c r="B92" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10981,30 +10977,39 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11012,10 +11017,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491079</v>
+        <v>491093</v>
       </c>
       <c r="R92" t="n">
-        <v>6943707</v>
+        <v>6943580</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11075,10 +11080,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121174644</v>
+        <v>121174973</v>
       </c>
       <c r="B93" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11110,7 +11115,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11127,10 +11132,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491320</v>
+        <v>491240</v>
       </c>
       <c r="R93" t="n">
-        <v>6943222</v>
+        <v>6943254</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11190,10 +11195,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121174651</v>
+        <v>121173037</v>
       </c>
       <c r="B94" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11202,39 +11207,30 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11242,10 +11238,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491092</v>
+        <v>491068</v>
       </c>
       <c r="R94" t="n">
-        <v>6943657</v>
+        <v>6943782</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11305,10 +11301,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121174670</v>
+        <v>121173006</v>
       </c>
       <c r="B95" t="n">
-        <v>79679</v>
+        <v>56563</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11317,30 +11313,39 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11348,10 +11353,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491078</v>
+        <v>491047</v>
       </c>
       <c r="R95" t="n">
-        <v>6943661</v>
+        <v>6943785</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11392,7 +11397,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11411,10 +11415,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121174619</v>
+        <v>121173047</v>
       </c>
       <c r="B96" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11446,7 +11450,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11463,10 +11467,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491336</v>
+        <v>491069</v>
       </c>
       <c r="R96" t="n">
-        <v>6943200</v>
+        <v>6943744</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11526,10 +11530,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121174716</v>
+        <v>121173058</v>
       </c>
       <c r="B97" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11538,39 +11542,30 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11578,10 +11573,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491104</v>
+        <v>491060</v>
       </c>
       <c r="R97" t="n">
-        <v>6943581</v>
+        <v>6943711</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11641,10 +11636,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121174710</v>
+        <v>121173118</v>
       </c>
       <c r="B98" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11693,10 +11688,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491099</v>
+        <v>491374</v>
       </c>
       <c r="R98" t="n">
-        <v>6943598</v>
+        <v>6943172</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11756,10 +11751,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121174660</v>
+        <v>121175104</v>
       </c>
       <c r="B99" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11794,11 +11789,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
@@ -11808,10 +11799,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491081</v>
+        <v>491240</v>
       </c>
       <c r="R99" t="n">
-        <v>6943657</v>
+        <v>6943272</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11871,10 +11862,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121174973</v>
+        <v>121174619</v>
       </c>
       <c r="B100" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11906,7 +11897,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -11923,10 +11914,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491240</v>
+        <v>491336</v>
       </c>
       <c r="R100" t="n">
-        <v>6943254</v>
+        <v>6943200</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11986,10 +11977,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121173006</v>
+        <v>121173088</v>
       </c>
       <c r="B101" t="n">
-        <v>56560</v>
+        <v>79682</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11998,39 +11989,30 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -12038,10 +12020,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491047</v>
+        <v>491154</v>
       </c>
       <c r="R101" t="n">
-        <v>6943785</v>
+        <v>6943740</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12082,6 +12064,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -12100,10 +12083,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121174681</v>
+        <v>121173066</v>
       </c>
       <c r="B102" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12112,39 +12095,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12152,10 +12126,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491091</v>
+        <v>491079</v>
       </c>
       <c r="R102" t="n">
-        <v>6943656</v>
+        <v>6943707</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12215,10 +12189,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121173118</v>
+        <v>121174644</v>
       </c>
       <c r="B103" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12267,10 +12241,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491374</v>
+        <v>491320</v>
       </c>
       <c r="R103" t="n">
-        <v>6943172</v>
+        <v>6943222</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12330,10 +12304,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121175104</v>
+        <v>121174651</v>
       </c>
       <c r="B104" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12365,10 +12339,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
@@ -12378,10 +12356,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491240</v>
+        <v>491092</v>
       </c>
       <c r="R104" t="n">
-        <v>6943272</v>
+        <v>6943657</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12441,10 +12419,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121173088</v>
+        <v>121173022</v>
       </c>
       <c r="B105" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12484,10 +12462,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491154</v>
+        <v>491045</v>
       </c>
       <c r="R105" t="n">
-        <v>6943740</v>
+        <v>6943777</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12547,10 +12525,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121174608</v>
+        <v>121174691</v>
       </c>
       <c r="B106" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12582,7 +12560,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12599,10 +12577,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491341</v>
+        <v>491088</v>
       </c>
       <c r="R106" t="n">
-        <v>6943167</v>
+        <v>6943643</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12662,10 +12640,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121174691</v>
+        <v>121174681</v>
       </c>
       <c r="B107" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12697,7 +12675,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12714,10 +12692,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491088</v>
+        <v>491091</v>
       </c>
       <c r="R107" t="n">
-        <v>6943643</v>
+        <v>6943656</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12777,10 +12755,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121173022</v>
+        <v>121174608</v>
       </c>
       <c r="B108" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12789,30 +12767,39 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -12820,10 +12807,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491045</v>
+        <v>491341</v>
       </c>
       <c r="R108" t="n">
-        <v>6943777</v>
+        <v>6943167</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12883,10 +12870,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121173037</v>
+        <v>121175096</v>
       </c>
       <c r="B109" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12895,41 +12882,50 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor -Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491068</v>
+        <v>491249</v>
       </c>
       <c r="R109" t="n">
-        <v>6943782</v>
+        <v>6943270</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12989,10 +12985,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121173047</v>
+        <v>121174638</v>
       </c>
       <c r="B110" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13024,7 +13020,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13041,10 +13037,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491069</v>
+        <v>491327</v>
       </c>
       <c r="R110" t="n">
-        <v>6943744</v>
+        <v>6943200</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13104,10 +13100,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121173054</v>
+        <v>121173075</v>
       </c>
       <c r="B111" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13147,10 +13143,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>491077</v>
+        <v>491094</v>
       </c>
       <c r="R111" t="n">
-        <v>6943749</v>
+        <v>6943719</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13210,10 +13206,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121173042</v>
+        <v>121174660</v>
       </c>
       <c r="B112" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13262,10 +13258,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>491060</v>
+        <v>491081</v>
       </c>
       <c r="R112" t="n">
-        <v>6943757</v>
+        <v>6943657</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13325,10 +13321,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121173030</v>
+        <v>121174703</v>
       </c>
       <c r="B113" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13337,30 +13333,39 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -13368,10 +13373,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>491061</v>
+        <v>491096</v>
       </c>
       <c r="R113" t="n">
-        <v>6943779</v>
+        <v>6943583</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13431,10 +13436,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121172997</v>
+        <v>121174670</v>
       </c>
       <c r="B114" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13474,10 +13479,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>491043</v>
+        <v>491078</v>
       </c>
       <c r="R114" t="n">
-        <v>6943791</v>
+        <v>6943661</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13510,11 +13515,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13542,10 +13542,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121174642</v>
+        <v>121173042</v>
       </c>
       <c r="B115" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13590,14 +13590,14 @@
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stor-lravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>491319</v>
+        <v>491060</v>
       </c>
       <c r="R115" t="n">
-        <v>6943212</v>
+        <v>6943757</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13657,10 +13657,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121174638</v>
+        <v>121174710</v>
       </c>
       <c r="B116" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -13709,10 +13709,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>491327</v>
+        <v>491099</v>
       </c>
       <c r="R116" t="n">
-        <v>6943200</v>
+        <v>6943598</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121174703</v>
+        <v>121173101</v>
       </c>
       <c r="B117" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13824,10 +13824,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>491096</v>
+        <v>491378</v>
       </c>
       <c r="R117" t="n">
-        <v>6943583</v>
+        <v>6943184</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -11195,10 +11195,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121173037</v>
+        <v>121173006</v>
       </c>
       <c r="B94" t="n">
-        <v>79682</v>
+        <v>56563</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11207,30 +11207,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11238,10 +11247,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491068</v>
+        <v>491047</v>
       </c>
       <c r="R94" t="n">
-        <v>6943782</v>
+        <v>6943785</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11282,7 +11291,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11301,10 +11309,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121173006</v>
+        <v>121173037</v>
       </c>
       <c r="B95" t="n">
-        <v>56563</v>
+        <v>79682</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11313,39 +11321,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11353,10 +11352,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491047</v>
+        <v>491068</v>
       </c>
       <c r="R95" t="n">
-        <v>6943785</v>
+        <v>6943782</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11397,6 +11396,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -10412,10 +10412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121174716</v>
+        <v>121172997</v>
       </c>
       <c r="B87" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10424,39 +10424,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10464,10 +10455,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491104</v>
+        <v>491043</v>
       </c>
       <c r="R87" t="n">
-        <v>6943581</v>
+        <v>6943791</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10500,6 +10491,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10527,10 +10523,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121174642</v>
+        <v>121173030</v>
       </c>
       <c r="B88" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10539,50 +10535,41 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-lravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491319</v>
+        <v>491061</v>
       </c>
       <c r="R88" t="n">
-        <v>6943212</v>
+        <v>6943779</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10642,10 +10629,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121172997</v>
+        <v>121174716</v>
       </c>
       <c r="B89" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10654,30 +10641,39 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10685,10 +10681,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491043</v>
+        <v>491104</v>
       </c>
       <c r="R89" t="n">
-        <v>6943791</v>
+        <v>6943581</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10721,11 +10717,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10753,10 +10744,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121173030</v>
+        <v>121174642</v>
       </c>
       <c r="B90" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10765,41 +10756,50 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor-lravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491061</v>
+        <v>491319</v>
       </c>
       <c r="R90" t="n">
-        <v>6943779</v>
+        <v>6943212</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -10412,10 +10412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121172997</v>
+        <v>121174638</v>
       </c>
       <c r="B87" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10424,30 +10424,39 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10455,10 +10464,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491043</v>
+        <v>491327</v>
       </c>
       <c r="R87" t="n">
-        <v>6943791</v>
+        <v>6943200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10491,11 +10500,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10523,10 +10527,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121173030</v>
+        <v>121173006</v>
       </c>
       <c r="B88" t="n">
-        <v>79682</v>
+        <v>56563</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10535,30 +10539,39 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10566,10 +10579,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491061</v>
+        <v>491047</v>
       </c>
       <c r="R88" t="n">
-        <v>6943779</v>
+        <v>6943785</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10610,7 +10623,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10629,10 +10641,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121174716</v>
+        <v>121173058</v>
       </c>
       <c r="B89" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10641,39 +10653,30 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10681,10 +10684,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491104</v>
+        <v>491060</v>
       </c>
       <c r="R89" t="n">
-        <v>6943581</v>
+        <v>6943711</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10744,10 +10747,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121174642</v>
+        <v>121173022</v>
       </c>
       <c r="B90" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10756,50 +10759,41 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-lravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491319</v>
+        <v>491045</v>
       </c>
       <c r="R90" t="n">
-        <v>6943212</v>
+        <v>6943777</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10859,10 +10853,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121173054</v>
+        <v>121173101</v>
       </c>
       <c r="B91" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10871,30 +10865,39 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10902,10 +10905,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491077</v>
+        <v>491378</v>
       </c>
       <c r="R91" t="n">
-        <v>6943749</v>
+        <v>6943184</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10965,10 +10968,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121174736</v>
+        <v>121173037</v>
       </c>
       <c r="B92" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10977,39 +10980,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11017,10 +11011,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491093</v>
+        <v>491068</v>
       </c>
       <c r="R92" t="n">
-        <v>6943580</v>
+        <v>6943782</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11080,10 +11074,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121174973</v>
+        <v>121173075</v>
       </c>
       <c r="B93" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11092,39 +11086,30 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11132,10 +11117,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491240</v>
+        <v>491094</v>
       </c>
       <c r="R93" t="n">
-        <v>6943254</v>
+        <v>6943719</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11195,10 +11180,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121173006</v>
+        <v>121174644</v>
       </c>
       <c r="B94" t="n">
-        <v>56563</v>
+        <v>98081</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11207,39 +11192,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11247,10 +11232,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491047</v>
+        <v>491320</v>
       </c>
       <c r="R94" t="n">
-        <v>6943785</v>
+        <v>6943222</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11291,6 +11276,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11309,10 +11295,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121173037</v>
+        <v>121175104</v>
       </c>
       <c r="B95" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11321,30 +11307,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11352,10 +11343,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491068</v>
+        <v>491240</v>
       </c>
       <c r="R95" t="n">
-        <v>6943782</v>
+        <v>6943272</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11415,7 +11406,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121173047</v>
+        <v>121173118</v>
       </c>
       <c r="B96" t="n">
         <v>98081</v>
@@ -11450,7 +11441,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11467,10 +11458,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491069</v>
+        <v>491374</v>
       </c>
       <c r="R96" t="n">
-        <v>6943744</v>
+        <v>6943172</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11530,10 +11521,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121173058</v>
+        <v>121174710</v>
       </c>
       <c r="B97" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11542,30 +11533,39 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11573,10 +11573,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491060</v>
+        <v>491099</v>
       </c>
       <c r="R97" t="n">
-        <v>6943711</v>
+        <v>6943598</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11636,7 +11636,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121173118</v>
+        <v>121174681</v>
       </c>
       <c r="B98" t="n">
         <v>98081</v>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11688,10 +11688,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491374</v>
+        <v>491091</v>
       </c>
       <c r="R98" t="n">
-        <v>6943172</v>
+        <v>6943656</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11751,7 +11751,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121175104</v>
+        <v>121174660</v>
       </c>
       <c r="B99" t="n">
         <v>98081</v>
@@ -11789,7 +11789,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
@@ -11799,10 +11803,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491240</v>
+        <v>491081</v>
       </c>
       <c r="R99" t="n">
-        <v>6943272</v>
+        <v>6943657</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11862,7 +11866,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121174619</v>
+        <v>121173047</v>
       </c>
       <c r="B100" t="n">
         <v>98081</v>
@@ -11897,7 +11901,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -11914,10 +11918,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491336</v>
+        <v>491069</v>
       </c>
       <c r="R100" t="n">
-        <v>6943200</v>
+        <v>6943744</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11977,10 +11981,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121173088</v>
+        <v>121174691</v>
       </c>
       <c r="B101" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11989,30 +11993,39 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -12020,10 +12033,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491154</v>
+        <v>491088</v>
       </c>
       <c r="R101" t="n">
-        <v>6943740</v>
+        <v>6943643</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12083,10 +12096,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121173066</v>
+        <v>121174716</v>
       </c>
       <c r="B102" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12095,30 +12108,39 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12126,10 +12148,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491079</v>
+        <v>491104</v>
       </c>
       <c r="R102" t="n">
-        <v>6943707</v>
+        <v>6943581</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12189,10 +12211,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121174644</v>
+        <v>121173030</v>
       </c>
       <c r="B103" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12201,39 +12223,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12241,10 +12254,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491320</v>
+        <v>491061</v>
       </c>
       <c r="R103" t="n">
-        <v>6943222</v>
+        <v>6943779</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12304,7 +12317,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121174651</v>
+        <v>121174703</v>
       </c>
       <c r="B104" t="n">
         <v>98081</v>
@@ -12339,7 +12352,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12356,10 +12369,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491092</v>
+        <v>491096</v>
       </c>
       <c r="R104" t="n">
-        <v>6943657</v>
+        <v>6943583</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12419,7 +12432,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121173022</v>
+        <v>121173054</v>
       </c>
       <c r="B105" t="n">
         <v>79682</v>
@@ -12462,10 +12475,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491045</v>
+        <v>491077</v>
       </c>
       <c r="R105" t="n">
-        <v>6943777</v>
+        <v>6943749</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12525,7 +12538,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121174691</v>
+        <v>121174619</v>
       </c>
       <c r="B106" t="n">
         <v>98081</v>
@@ -12577,10 +12590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491088</v>
+        <v>491336</v>
       </c>
       <c r="R106" t="n">
-        <v>6943643</v>
+        <v>6943200</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12640,10 +12653,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121174681</v>
+        <v>121172997</v>
       </c>
       <c r="B107" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12652,39 +12665,30 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -12692,10 +12696,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491091</v>
+        <v>491043</v>
       </c>
       <c r="R107" t="n">
-        <v>6943656</v>
+        <v>6943791</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12728,6 +12732,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12870,7 +12879,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121175096</v>
+        <v>121174973</v>
       </c>
       <c r="B109" t="n">
         <v>98081</v>
@@ -12918,14 +12927,14 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stor -Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491249</v>
+        <v>491240</v>
       </c>
       <c r="R109" t="n">
-        <v>6943270</v>
+        <v>6943254</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12985,10 +12994,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121174638</v>
+        <v>121173088</v>
       </c>
       <c r="B110" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12997,39 +13006,30 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13037,10 +13037,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491327</v>
+        <v>491154</v>
       </c>
       <c r="R110" t="n">
-        <v>6943200</v>
+        <v>6943740</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121173075</v>
+        <v>121174670</v>
       </c>
       <c r="B111" t="n">
         <v>79682</v>
@@ -13143,10 +13143,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>491094</v>
+        <v>491078</v>
       </c>
       <c r="R111" t="n">
-        <v>6943719</v>
+        <v>6943661</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13206,7 +13206,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121174660</v>
+        <v>121174642</v>
       </c>
       <c r="B112" t="n">
         <v>98081</v>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13254,14 +13254,14 @@
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor-lravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>491081</v>
+        <v>491319</v>
       </c>
       <c r="R112" t="n">
-        <v>6943657</v>
+        <v>6943212</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13321,10 +13321,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121174703</v>
+        <v>121173066</v>
       </c>
       <c r="B113" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13333,39 +13333,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -13373,10 +13364,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>491096</v>
+        <v>491079</v>
       </c>
       <c r="R113" t="n">
-        <v>6943583</v>
+        <v>6943707</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13436,10 +13427,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121174670</v>
+        <v>121174736</v>
       </c>
       <c r="B114" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13448,30 +13439,39 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -13479,10 +13479,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>491078</v>
+        <v>491093</v>
       </c>
       <c r="R114" t="n">
-        <v>6943661</v>
+        <v>6943580</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13657,7 +13657,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121174710</v>
+        <v>121175096</v>
       </c>
       <c r="B116" t="n">
         <v>98081</v>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -13705,14 +13705,14 @@
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor -Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>491099</v>
+        <v>491249</v>
       </c>
       <c r="R116" t="n">
-        <v>6943598</v>
+        <v>6943270</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13772,7 +13772,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121173101</v>
+        <v>121174651</v>
       </c>
       <c r="B117" t="n">
         <v>98081</v>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -13824,10 +13824,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>491378</v>
+        <v>491092</v>
       </c>
       <c r="R117" t="n">
-        <v>6943184</v>
+        <v>6943657</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -12096,10 +12096,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121174716</v>
+        <v>121173030</v>
       </c>
       <c r="B102" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12108,39 +12108,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12148,10 +12139,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491104</v>
+        <v>491061</v>
       </c>
       <c r="R102" t="n">
-        <v>6943581</v>
+        <v>6943779</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12211,10 +12202,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121173030</v>
+        <v>121174716</v>
       </c>
       <c r="B103" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12223,30 +12214,39 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12254,10 +12254,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491061</v>
+        <v>491104</v>
       </c>
       <c r="R103" t="n">
-        <v>6943779</v>
+        <v>6943581</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -10412,10 +10412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121174638</v>
+        <v>121173066</v>
       </c>
       <c r="B87" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10424,39 +10424,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10464,10 +10455,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491327</v>
+        <v>491079</v>
       </c>
       <c r="R87" t="n">
-        <v>6943200</v>
+        <v>6943707</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10527,10 +10518,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121173006</v>
+        <v>121174670</v>
       </c>
       <c r="B88" t="n">
-        <v>56563</v>
+        <v>79685</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10539,39 +10530,30 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10579,10 +10561,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491047</v>
+        <v>491078</v>
       </c>
       <c r="R88" t="n">
-        <v>6943785</v>
+        <v>6943661</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10623,6 +10605,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10641,10 +10624,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121173058</v>
+        <v>121174608</v>
       </c>
       <c r="B89" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10653,30 +10636,39 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10684,10 +10676,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491060</v>
+        <v>491341</v>
       </c>
       <c r="R89" t="n">
-        <v>6943711</v>
+        <v>6943167</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10747,10 +10739,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121173022</v>
+        <v>121174716</v>
       </c>
       <c r="B90" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10759,30 +10751,39 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10790,10 +10791,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491045</v>
+        <v>491104</v>
       </c>
       <c r="R90" t="n">
-        <v>6943777</v>
+        <v>6943581</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10853,10 +10854,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121173101</v>
+        <v>121173058</v>
       </c>
       <c r="B91" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10865,39 +10866,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10905,10 +10897,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491378</v>
+        <v>491060</v>
       </c>
       <c r="R91" t="n">
-        <v>6943184</v>
+        <v>6943711</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10968,10 +10960,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121173037</v>
+        <v>121174619</v>
       </c>
       <c r="B92" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10980,30 +10972,39 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11011,10 +11012,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491068</v>
+        <v>491336</v>
       </c>
       <c r="R92" t="n">
-        <v>6943782</v>
+        <v>6943200</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11074,10 +11075,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121173075</v>
+        <v>121173030</v>
       </c>
       <c r="B93" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11117,10 +11118,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491094</v>
+        <v>491061</v>
       </c>
       <c r="R93" t="n">
-        <v>6943719</v>
+        <v>6943779</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11180,10 +11181,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121174644</v>
+        <v>121174973</v>
       </c>
       <c r="B94" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11215,7 +11216,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11232,10 +11233,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491320</v>
+        <v>491240</v>
       </c>
       <c r="R94" t="n">
-        <v>6943222</v>
+        <v>6943254</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11295,10 +11296,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121175104</v>
+        <v>121174710</v>
       </c>
       <c r="B95" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11330,10 +11331,14 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
@@ -11343,10 +11348,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491240</v>
+        <v>491099</v>
       </c>
       <c r="R95" t="n">
-        <v>6943272</v>
+        <v>6943598</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11406,10 +11411,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121173118</v>
+        <v>121174736</v>
       </c>
       <c r="B96" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11441,7 +11446,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11458,10 +11463,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491374</v>
+        <v>491093</v>
       </c>
       <c r="R96" t="n">
-        <v>6943172</v>
+        <v>6943580</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11521,10 +11526,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121174710</v>
+        <v>121173101</v>
       </c>
       <c r="B97" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11556,7 +11561,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11573,10 +11578,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491099</v>
+        <v>491378</v>
       </c>
       <c r="R97" t="n">
-        <v>6943598</v>
+        <v>6943184</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11636,10 +11641,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121174681</v>
+        <v>121174651</v>
       </c>
       <c r="B98" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11688,10 +11693,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491091</v>
+        <v>491092</v>
       </c>
       <c r="R98" t="n">
-        <v>6943656</v>
+        <v>6943657</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11751,10 +11756,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121174660</v>
+        <v>121174703</v>
       </c>
       <c r="B99" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11803,10 +11808,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491081</v>
+        <v>491096</v>
       </c>
       <c r="R99" t="n">
-        <v>6943657</v>
+        <v>6943583</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11866,10 +11871,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121173047</v>
+        <v>121172997</v>
       </c>
       <c r="B100" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11878,39 +11883,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11918,10 +11914,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491069</v>
+        <v>491043</v>
       </c>
       <c r="R100" t="n">
-        <v>6943744</v>
+        <v>6943791</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11954,6 +11950,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11981,10 +11982,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121174691</v>
+        <v>121173022</v>
       </c>
       <c r="B101" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11993,39 +11994,30 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -12033,10 +12025,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491088</v>
+        <v>491045</v>
       </c>
       <c r="R101" t="n">
-        <v>6943643</v>
+        <v>6943777</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12096,10 +12088,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121173030</v>
+        <v>121173006</v>
       </c>
       <c r="B102" t="n">
-        <v>79682</v>
+        <v>56563</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12108,30 +12100,39 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12139,10 +12140,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491061</v>
+        <v>491047</v>
       </c>
       <c r="R102" t="n">
-        <v>6943779</v>
+        <v>6943785</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12183,7 +12184,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12202,10 +12202,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121174716</v>
+        <v>121173075</v>
       </c>
       <c r="B103" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12214,39 +12214,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12254,10 +12245,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491104</v>
+        <v>491094</v>
       </c>
       <c r="R103" t="n">
-        <v>6943581</v>
+        <v>6943719</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12317,10 +12308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121174703</v>
+        <v>121173118</v>
       </c>
       <c r="B104" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12352,7 +12343,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12369,10 +12360,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491096</v>
+        <v>491374</v>
       </c>
       <c r="R104" t="n">
-        <v>6943583</v>
+        <v>6943172</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12432,10 +12423,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121173054</v>
+        <v>121174644</v>
       </c>
       <c r="B105" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12444,30 +12435,39 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491077</v>
+        <v>491320</v>
       </c>
       <c r="R105" t="n">
-        <v>6943749</v>
+        <v>6943222</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12538,10 +12538,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121174619</v>
+        <v>121174638</v>
       </c>
       <c r="B106" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491336</v>
+        <v>491327</v>
       </c>
       <c r="R106" t="n">
         <v>6943200</v>
@@ -12653,10 +12653,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121172997</v>
+        <v>121173088</v>
       </c>
       <c r="B107" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12696,10 +12696,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491043</v>
+        <v>491154</v>
       </c>
       <c r="R107" t="n">
-        <v>6943791</v>
+        <v>6943740</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12732,11 +12732,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12764,10 +12759,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121174608</v>
+        <v>121174642</v>
       </c>
       <c r="B108" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12799,7 +12794,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -12812,14 +12807,14 @@
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor-lravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491341</v>
+        <v>491319</v>
       </c>
       <c r="R108" t="n">
-        <v>6943167</v>
+        <v>6943212</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12879,10 +12874,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121174973</v>
+        <v>121174681</v>
       </c>
       <c r="B109" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12914,7 +12909,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -12931,10 +12926,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491240</v>
+        <v>491091</v>
       </c>
       <c r="R109" t="n">
-        <v>6943254</v>
+        <v>6943656</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12994,10 +12989,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121173088</v>
+        <v>121173054</v>
       </c>
       <c r="B110" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13037,10 +13032,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491154</v>
+        <v>491077</v>
       </c>
       <c r="R110" t="n">
-        <v>6943740</v>
+        <v>6943749</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13100,10 +13095,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121174670</v>
+        <v>121173037</v>
       </c>
       <c r="B111" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13143,10 +13138,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>491078</v>
+        <v>491068</v>
       </c>
       <c r="R111" t="n">
-        <v>6943661</v>
+        <v>6943782</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13206,10 +13201,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121174642</v>
+        <v>121174691</v>
       </c>
       <c r="B112" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13241,7 +13236,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13254,14 +13249,14 @@
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stor-lravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>491319</v>
+        <v>491088</v>
       </c>
       <c r="R112" t="n">
-        <v>6943212</v>
+        <v>6943643</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13321,10 +13316,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121173066</v>
+        <v>121173047</v>
       </c>
       <c r="B113" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13333,30 +13328,39 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -13364,10 +13368,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>491079</v>
+        <v>491069</v>
       </c>
       <c r="R113" t="n">
-        <v>6943707</v>
+        <v>6943744</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13427,10 +13431,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121174736</v>
+        <v>121175104</v>
       </c>
       <c r="B114" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13465,11 +13469,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
@@ -13479,10 +13479,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>491093</v>
+        <v>491240</v>
       </c>
       <c r="R114" t="n">
-        <v>6943580</v>
+        <v>6943272</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13545,7 +13545,7 @@
         <v>121173042</v>
       </c>
       <c r="B115" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>121175096</v>
       </c>
       <c r="B116" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121174651</v>
+        <v>121174660</v>
       </c>
       <c r="B117" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>491092</v>
+        <v>491081</v>
       </c>
       <c r="R117" t="n">
         <v>6943657</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -10412,10 +10412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121173066</v>
+        <v>121174736</v>
       </c>
       <c r="B87" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10424,30 +10424,39 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10455,10 +10464,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491079</v>
+        <v>491093</v>
       </c>
       <c r="R87" t="n">
-        <v>6943707</v>
+        <v>6943580</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10518,7 +10527,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121174670</v>
+        <v>121173030</v>
       </c>
       <c r="B88" t="n">
         <v>79685</v>
@@ -10561,10 +10570,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491078</v>
+        <v>491061</v>
       </c>
       <c r="R88" t="n">
-        <v>6943661</v>
+        <v>6943779</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10624,10 +10633,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121174608</v>
+        <v>121174651</v>
       </c>
       <c r="B89" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10659,7 +10668,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10676,10 +10685,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491341</v>
+        <v>491092</v>
       </c>
       <c r="R89" t="n">
-        <v>6943167</v>
+        <v>6943657</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10739,10 +10748,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121174716</v>
+        <v>121174973</v>
       </c>
       <c r="B90" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10791,10 +10800,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491104</v>
+        <v>491240</v>
       </c>
       <c r="R90" t="n">
-        <v>6943581</v>
+        <v>6943254</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10854,10 +10863,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121173058</v>
+        <v>121174691</v>
       </c>
       <c r="B91" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10866,30 +10875,39 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10897,10 +10915,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491060</v>
+        <v>491088</v>
       </c>
       <c r="R91" t="n">
-        <v>6943711</v>
+        <v>6943643</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10960,10 +10978,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121174619</v>
+        <v>121173042</v>
       </c>
       <c r="B92" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10995,7 +11013,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11012,10 +11030,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491336</v>
+        <v>491060</v>
       </c>
       <c r="R92" t="n">
-        <v>6943200</v>
+        <v>6943757</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11075,10 +11093,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121173030</v>
+        <v>121175096</v>
       </c>
       <c r="B93" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11087,41 +11105,50 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor -Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491061</v>
+        <v>491249</v>
       </c>
       <c r="R93" t="n">
-        <v>6943779</v>
+        <v>6943270</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11181,10 +11208,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121174973</v>
+        <v>121174644</v>
       </c>
       <c r="B94" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11216,7 +11243,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11233,10 +11260,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491240</v>
+        <v>491320</v>
       </c>
       <c r="R94" t="n">
-        <v>6943254</v>
+        <v>6943222</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11296,10 +11323,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121174710</v>
+        <v>121173054</v>
       </c>
       <c r="B95" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11308,39 +11335,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11348,10 +11366,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491099</v>
+        <v>491077</v>
       </c>
       <c r="R95" t="n">
-        <v>6943598</v>
+        <v>6943749</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11411,10 +11429,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121174736</v>
+        <v>121173066</v>
       </c>
       <c r="B96" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11423,39 +11441,30 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11463,10 +11472,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491093</v>
+        <v>491079</v>
       </c>
       <c r="R96" t="n">
-        <v>6943580</v>
+        <v>6943707</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11526,10 +11535,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121173101</v>
+        <v>121174681</v>
       </c>
       <c r="B97" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11561,7 +11570,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11578,10 +11587,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491378</v>
+        <v>491091</v>
       </c>
       <c r="R97" t="n">
-        <v>6943184</v>
+        <v>6943656</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11641,10 +11650,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121174651</v>
+        <v>121174638</v>
       </c>
       <c r="B98" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11676,7 +11685,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11693,10 +11702,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491092</v>
+        <v>491327</v>
       </c>
       <c r="R98" t="n">
-        <v>6943657</v>
+        <v>6943200</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11756,10 +11765,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121174703</v>
+        <v>121174608</v>
       </c>
       <c r="B99" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11808,10 +11817,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491096</v>
+        <v>491341</v>
       </c>
       <c r="R99" t="n">
-        <v>6943583</v>
+        <v>6943167</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11871,10 +11880,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121172997</v>
+        <v>121174716</v>
       </c>
       <c r="B100" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11883,30 +11892,39 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11914,10 +11932,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491043</v>
+        <v>491104</v>
       </c>
       <c r="R100" t="n">
-        <v>6943791</v>
+        <v>6943581</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11950,11 +11968,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11982,10 +11995,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121173022</v>
+        <v>121174710</v>
       </c>
       <c r="B101" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11994,30 +12007,39 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -12025,10 +12047,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491045</v>
+        <v>491099</v>
       </c>
       <c r="R101" t="n">
-        <v>6943777</v>
+        <v>6943598</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12088,10 +12110,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121173006</v>
+        <v>121174660</v>
       </c>
       <c r="B102" t="n">
-        <v>56563</v>
+        <v>98095</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12100,39 +12122,39 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12140,10 +12162,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491047</v>
+        <v>491081</v>
       </c>
       <c r="R102" t="n">
-        <v>6943785</v>
+        <v>6943657</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12184,6 +12206,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12202,7 +12225,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121173075</v>
+        <v>121173022</v>
       </c>
       <c r="B103" t="n">
         <v>79685</v>
@@ -12245,10 +12268,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491094</v>
+        <v>491045</v>
       </c>
       <c r="R103" t="n">
-        <v>6943719</v>
+        <v>6943777</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12308,10 +12331,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121173118</v>
+        <v>121174642</v>
       </c>
       <c r="B104" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12343,7 +12366,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12356,14 +12379,14 @@
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor-lravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491374</v>
+        <v>491319</v>
       </c>
       <c r="R104" t="n">
-        <v>6943172</v>
+        <v>6943212</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12423,10 +12446,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121174644</v>
+        <v>121173088</v>
       </c>
       <c r="B105" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12435,39 +12458,30 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -12475,10 +12489,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491320</v>
+        <v>491154</v>
       </c>
       <c r="R105" t="n">
-        <v>6943222</v>
+        <v>6943740</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12538,10 +12552,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121174638</v>
+        <v>121174619</v>
       </c>
       <c r="B106" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12573,7 +12587,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12590,7 +12604,7 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491327</v>
+        <v>491336</v>
       </c>
       <c r="R106" t="n">
         <v>6943200</v>
@@ -12653,7 +12667,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121173088</v>
+        <v>121173058</v>
       </c>
       <c r="B107" t="n">
         <v>79685</v>
@@ -12696,10 +12710,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491154</v>
+        <v>491060</v>
       </c>
       <c r="R107" t="n">
-        <v>6943740</v>
+        <v>6943711</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12759,10 +12773,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121174642</v>
+        <v>121172997</v>
       </c>
       <c r="B108" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12771,50 +12785,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-lravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491319</v>
+        <v>491043</v>
       </c>
       <c r="R108" t="n">
-        <v>6943212</v>
+        <v>6943791</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12847,6 +12852,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12874,10 +12884,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121174681</v>
+        <v>121173037</v>
       </c>
       <c r="B109" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12886,39 +12896,30 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -12926,10 +12927,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491091</v>
+        <v>491068</v>
       </c>
       <c r="R109" t="n">
-        <v>6943656</v>
+        <v>6943782</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12989,10 +12990,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121173054</v>
+        <v>121173006</v>
       </c>
       <c r="B110" t="n">
-        <v>79685</v>
+        <v>56563</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13001,30 +13002,39 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13032,10 +13042,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491077</v>
+        <v>491047</v>
       </c>
       <c r="R110" t="n">
-        <v>6943749</v>
+        <v>6943785</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13076,7 +13086,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -13095,10 +13104,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121173037</v>
+        <v>121173047</v>
       </c>
       <c r="B111" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13107,30 +13116,39 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -13138,10 +13156,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>491068</v>
+        <v>491069</v>
       </c>
       <c r="R111" t="n">
-        <v>6943782</v>
+        <v>6943744</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13201,10 +13219,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121174691</v>
+        <v>121173075</v>
       </c>
       <c r="B112" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13213,39 +13231,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13253,10 +13262,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>491088</v>
+        <v>491094</v>
       </c>
       <c r="R112" t="n">
-        <v>6943643</v>
+        <v>6943719</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13316,10 +13325,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121173047</v>
+        <v>121173101</v>
       </c>
       <c r="B113" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13351,7 +13360,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13368,10 +13377,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>491069</v>
+        <v>491378</v>
       </c>
       <c r="R113" t="n">
-        <v>6943744</v>
+        <v>6943184</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13431,10 +13440,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121175104</v>
+        <v>121174670</v>
       </c>
       <c r="B114" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13443,35 +13452,30 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -13479,10 +13483,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>491240</v>
+        <v>491078</v>
       </c>
       <c r="R114" t="n">
-        <v>6943272</v>
+        <v>6943661</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13542,10 +13546,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121173042</v>
+        <v>121173118</v>
       </c>
       <c r="B115" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13577,7 +13581,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13594,10 +13598,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>491060</v>
+        <v>491374</v>
       </c>
       <c r="R115" t="n">
-        <v>6943757</v>
+        <v>6943172</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13657,10 +13661,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121175096</v>
+        <v>121175104</v>
       </c>
       <c r="B116" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13695,24 +13699,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stor -Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>491249</v>
+        <v>491240</v>
       </c>
       <c r="R116" t="n">
-        <v>6943270</v>
+        <v>6943272</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121174660</v>
+        <v>121174703</v>
       </c>
       <c r="B117" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13824,10 +13824,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>491081</v>
+        <v>491096</v>
       </c>
       <c r="R117" t="n">
-        <v>6943657</v>
+        <v>6943583</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -10412,10 +10412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121174736</v>
+        <v>121174638</v>
       </c>
       <c r="B87" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491093</v>
+        <v>491327</v>
       </c>
       <c r="R87" t="n">
-        <v>6943580</v>
+        <v>6943200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10527,10 +10527,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121173030</v>
+        <v>121172997</v>
       </c>
       <c r="B88" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491061</v>
+        <v>491043</v>
       </c>
       <c r="R88" t="n">
-        <v>6943779</v>
+        <v>6943791</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10606,6 +10606,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10633,10 +10638,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121174651</v>
+        <v>121174710</v>
       </c>
       <c r="B89" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10668,7 +10673,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10685,10 +10690,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491092</v>
+        <v>491099</v>
       </c>
       <c r="R89" t="n">
-        <v>6943657</v>
+        <v>6943598</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10748,10 +10753,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121174973</v>
+        <v>121173006</v>
       </c>
       <c r="B90" t="n">
-        <v>98095</v>
+        <v>56566</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10760,39 +10765,39 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10800,10 +10805,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491240</v>
+        <v>491047</v>
       </c>
       <c r="R90" t="n">
-        <v>6943254</v>
+        <v>6943785</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10844,7 +10849,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10863,10 +10867,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121174691</v>
+        <v>121174651</v>
       </c>
       <c r="B91" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10898,7 +10902,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10915,10 +10919,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491088</v>
+        <v>491092</v>
       </c>
       <c r="R91" t="n">
-        <v>6943643</v>
+        <v>6943657</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10978,10 +10982,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121173042</v>
+        <v>121173066</v>
       </c>
       <c r="B92" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10990,39 +10994,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11030,10 +11025,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491060</v>
+        <v>491079</v>
       </c>
       <c r="R92" t="n">
-        <v>6943757</v>
+        <v>6943707</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11093,10 +11088,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121175096</v>
+        <v>121173058</v>
       </c>
       <c r="B93" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11105,50 +11100,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor -Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491249</v>
+        <v>491060</v>
       </c>
       <c r="R93" t="n">
-        <v>6943270</v>
+        <v>6943711</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11208,10 +11194,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121174644</v>
+        <v>121173088</v>
       </c>
       <c r="B94" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11220,39 +11206,30 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11260,10 +11237,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491320</v>
+        <v>491154</v>
       </c>
       <c r="R94" t="n">
-        <v>6943222</v>
+        <v>6943740</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11323,10 +11300,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121173054</v>
+        <v>121173047</v>
       </c>
       <c r="B95" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11335,30 +11312,39 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11366,10 +11352,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491077</v>
+        <v>491069</v>
       </c>
       <c r="R95" t="n">
-        <v>6943749</v>
+        <v>6943744</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11429,10 +11415,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121173066</v>
+        <v>121174716</v>
       </c>
       <c r="B96" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11441,30 +11427,39 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11472,10 +11467,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491079</v>
+        <v>491104</v>
       </c>
       <c r="R96" t="n">
-        <v>6943707</v>
+        <v>6943581</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11535,10 +11530,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121174681</v>
+        <v>121173118</v>
       </c>
       <c r="B97" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11570,7 +11565,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11587,10 +11582,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491091</v>
+        <v>491374</v>
       </c>
       <c r="R97" t="n">
-        <v>6943656</v>
+        <v>6943172</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11650,10 +11645,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121174638</v>
+        <v>121174619</v>
       </c>
       <c r="B98" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11685,7 +11680,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11702,7 +11697,7 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491327</v>
+        <v>491336</v>
       </c>
       <c r="R98" t="n">
         <v>6943200</v>
@@ -11765,10 +11760,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121174608</v>
+        <v>121173022</v>
       </c>
       <c r="B99" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11777,39 +11772,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11817,10 +11803,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491341</v>
+        <v>491045</v>
       </c>
       <c r="R99" t="n">
-        <v>6943167</v>
+        <v>6943777</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11880,10 +11866,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121174716</v>
+        <v>121174642</v>
       </c>
       <c r="B100" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11915,7 +11901,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -11928,14 +11914,14 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor-lravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491104</v>
+        <v>491319</v>
       </c>
       <c r="R100" t="n">
-        <v>6943581</v>
+        <v>6943212</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11995,10 +11981,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121174710</v>
+        <v>121173101</v>
       </c>
       <c r="B101" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12030,7 +12016,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12047,10 +12033,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491099</v>
+        <v>491378</v>
       </c>
       <c r="R101" t="n">
-        <v>6943598</v>
+        <v>6943184</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12110,10 +12096,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121174660</v>
+        <v>121173037</v>
       </c>
       <c r="B102" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12122,39 +12108,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12162,10 +12139,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491081</v>
+        <v>491068</v>
       </c>
       <c r="R102" t="n">
-        <v>6943657</v>
+        <v>6943782</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12225,10 +12202,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121173022</v>
+        <v>121174973</v>
       </c>
       <c r="B103" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12237,30 +12214,39 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12268,10 +12254,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491045</v>
+        <v>491240</v>
       </c>
       <c r="R103" t="n">
-        <v>6943777</v>
+        <v>6943254</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12331,10 +12317,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121174642</v>
+        <v>121173075</v>
       </c>
       <c r="B104" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12343,50 +12329,41 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stor-lravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491319</v>
+        <v>491094</v>
       </c>
       <c r="R104" t="n">
-        <v>6943212</v>
+        <v>6943719</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12446,10 +12423,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121173088</v>
+        <v>121174670</v>
       </c>
       <c r="B105" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12489,10 +12466,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491154</v>
+        <v>491078</v>
       </c>
       <c r="R105" t="n">
-        <v>6943740</v>
+        <v>6943661</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12552,10 +12529,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121174619</v>
+        <v>121174644</v>
       </c>
       <c r="B106" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12604,10 +12581,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491336</v>
+        <v>491320</v>
       </c>
       <c r="R106" t="n">
-        <v>6943200</v>
+        <v>6943222</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12667,10 +12644,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121173058</v>
+        <v>121174736</v>
       </c>
       <c r="B107" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12679,30 +12656,39 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -12710,10 +12696,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491060</v>
+        <v>491093</v>
       </c>
       <c r="R107" t="n">
-        <v>6943711</v>
+        <v>6943580</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12773,10 +12759,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121172997</v>
+        <v>121175096</v>
       </c>
       <c r="B108" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12785,41 +12771,50 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor -Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491043</v>
+        <v>491249</v>
       </c>
       <c r="R108" t="n">
-        <v>6943791</v>
+        <v>6943270</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12852,11 +12847,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12884,10 +12874,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121173037</v>
+        <v>121174681</v>
       </c>
       <c r="B109" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12896,30 +12886,39 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -12927,10 +12926,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491068</v>
+        <v>491091</v>
       </c>
       <c r="R109" t="n">
-        <v>6943782</v>
+        <v>6943656</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12990,10 +12989,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121173006</v>
+        <v>121173042</v>
       </c>
       <c r="B110" t="n">
-        <v>56563</v>
+        <v>98098</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13002,39 +13001,39 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13042,10 +13041,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491047</v>
+        <v>491060</v>
       </c>
       <c r="R110" t="n">
-        <v>6943785</v>
+        <v>6943757</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13086,6 +13085,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -13104,10 +13104,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121173047</v>
+        <v>121174691</v>
       </c>
       <c r="B111" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>491069</v>
+        <v>491088</v>
       </c>
       <c r="R111" t="n">
-        <v>6943744</v>
+        <v>6943643</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13219,10 +13219,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121173075</v>
+        <v>121174660</v>
       </c>
       <c r="B112" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13231,30 +13231,39 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13262,10 +13271,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>491094</v>
+        <v>491081</v>
       </c>
       <c r="R112" t="n">
-        <v>6943719</v>
+        <v>6943657</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13325,10 +13334,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121173101</v>
+        <v>121174703</v>
       </c>
       <c r="B113" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13377,10 +13386,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>491378</v>
+        <v>491096</v>
       </c>
       <c r="R113" t="n">
-        <v>6943184</v>
+        <v>6943583</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13440,10 +13449,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121174670</v>
+        <v>121175104</v>
       </c>
       <c r="B114" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13452,30 +13461,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -13483,10 +13497,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>491078</v>
+        <v>491240</v>
       </c>
       <c r="R114" t="n">
-        <v>6943661</v>
+        <v>6943272</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13546,10 +13560,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121173118</v>
+        <v>121173054</v>
       </c>
       <c r="B115" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13558,39 +13572,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -13598,10 +13603,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>491374</v>
+        <v>491077</v>
       </c>
       <c r="R115" t="n">
-        <v>6943172</v>
+        <v>6943749</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13661,10 +13666,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121175104</v>
+        <v>121174608</v>
       </c>
       <c r="B116" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13699,7 +13704,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
@@ -13709,10 +13718,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>491240</v>
+        <v>491341</v>
       </c>
       <c r="R116" t="n">
-        <v>6943272</v>
+        <v>6943167</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13772,10 +13781,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121174703</v>
+        <v>121173030</v>
       </c>
       <c r="B117" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13784,39 +13793,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13824,10 +13824,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>491096</v>
+        <v>491061</v>
       </c>
       <c r="R117" t="n">
-        <v>6943583</v>
+        <v>6943779</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -10412,7 +10412,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121174638</v>
+        <v>121175104</v>
       </c>
       <c r="B87" t="n">
         <v>98098</v>
@@ -10450,11 +10450,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
@@ -10464,10 +10460,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491327</v>
+        <v>491240</v>
       </c>
       <c r="R87" t="n">
-        <v>6943200</v>
+        <v>6943272</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10527,7 +10523,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121172997</v>
+        <v>121173058</v>
       </c>
       <c r="B88" t="n">
         <v>79688</v>
@@ -10570,10 +10566,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491043</v>
+        <v>491060</v>
       </c>
       <c r="R88" t="n">
-        <v>6943791</v>
+        <v>6943711</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10606,11 +10602,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10638,10 +10629,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121174710</v>
+        <v>121173030</v>
       </c>
       <c r="B89" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10650,39 +10641,30 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10690,10 +10672,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491099</v>
+        <v>491061</v>
       </c>
       <c r="R89" t="n">
-        <v>6943598</v>
+        <v>6943779</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10753,10 +10735,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121173006</v>
+        <v>121174651</v>
       </c>
       <c r="B90" t="n">
-        <v>56566</v>
+        <v>98098</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10765,39 +10747,39 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10805,10 +10787,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491047</v>
+        <v>491092</v>
       </c>
       <c r="R90" t="n">
-        <v>6943785</v>
+        <v>6943657</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10849,6 +10831,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10867,10 +10850,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121174651</v>
+        <v>121173037</v>
       </c>
       <c r="B91" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10879,39 +10862,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10919,10 +10893,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491092</v>
+        <v>491068</v>
       </c>
       <c r="R91" t="n">
-        <v>6943657</v>
+        <v>6943782</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10982,10 +10956,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121173066</v>
+        <v>121174736</v>
       </c>
       <c r="B92" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10994,30 +10968,39 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11025,10 +11008,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491079</v>
+        <v>491093</v>
       </c>
       <c r="R92" t="n">
-        <v>6943707</v>
+        <v>6943580</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11088,10 +11071,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121173058</v>
+        <v>121174660</v>
       </c>
       <c r="B93" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11100,30 +11083,39 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11131,10 +11123,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491060</v>
+        <v>491081</v>
       </c>
       <c r="R93" t="n">
-        <v>6943711</v>
+        <v>6943657</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11194,7 +11186,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121173088</v>
+        <v>121173022</v>
       </c>
       <c r="B94" t="n">
         <v>79688</v>
@@ -11237,10 +11229,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491154</v>
+        <v>491045</v>
       </c>
       <c r="R94" t="n">
-        <v>6943740</v>
+        <v>6943777</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11300,7 +11292,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121173047</v>
+        <v>121174619</v>
       </c>
       <c r="B95" t="n">
         <v>98098</v>
@@ -11335,7 +11327,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11352,10 +11344,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491069</v>
+        <v>491336</v>
       </c>
       <c r="R95" t="n">
-        <v>6943744</v>
+        <v>6943200</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11415,7 +11407,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121174716</v>
+        <v>121174710</v>
       </c>
       <c r="B96" t="n">
         <v>98098</v>
@@ -11450,7 +11442,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11467,10 +11459,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491104</v>
+        <v>491099</v>
       </c>
       <c r="R96" t="n">
-        <v>6943581</v>
+        <v>6943598</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11530,10 +11522,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121173118</v>
+        <v>121173006</v>
       </c>
       <c r="B97" t="n">
-        <v>98098</v>
+        <v>56566</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11542,39 +11534,39 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11582,10 +11574,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491374</v>
+        <v>491047</v>
       </c>
       <c r="R97" t="n">
-        <v>6943172</v>
+        <v>6943785</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11626,7 +11618,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11645,10 +11636,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121174619</v>
+        <v>121172997</v>
       </c>
       <c r="B98" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11657,39 +11648,30 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11697,10 +11679,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491336</v>
+        <v>491043</v>
       </c>
       <c r="R98" t="n">
-        <v>6943200</v>
+        <v>6943791</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11733,6 +11715,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11760,10 +11747,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121173022</v>
+        <v>121174681</v>
       </c>
       <c r="B99" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11772,30 +11759,39 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11803,10 +11799,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491045</v>
+        <v>491091</v>
       </c>
       <c r="R99" t="n">
-        <v>6943777</v>
+        <v>6943656</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12096,10 +12092,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121173037</v>
+        <v>121174608</v>
       </c>
       <c r="B102" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12108,30 +12104,39 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12139,10 +12144,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491068</v>
+        <v>491341</v>
       </c>
       <c r="R102" t="n">
-        <v>6943782</v>
+        <v>6943167</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12202,7 +12207,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121174973</v>
+        <v>121174703</v>
       </c>
       <c r="B103" t="n">
         <v>98098</v>
@@ -12254,10 +12259,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491240</v>
+        <v>491096</v>
       </c>
       <c r="R103" t="n">
-        <v>6943254</v>
+        <v>6943583</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12317,10 +12322,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121173075</v>
+        <v>121174973</v>
       </c>
       <c r="B104" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12329,30 +12334,39 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12360,10 +12374,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491094</v>
+        <v>491240</v>
       </c>
       <c r="R104" t="n">
-        <v>6943719</v>
+        <v>6943254</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12423,7 +12437,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121174670</v>
+        <v>121173088</v>
       </c>
       <c r="B105" t="n">
         <v>79688</v>
@@ -12466,10 +12480,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491078</v>
+        <v>491154</v>
       </c>
       <c r="R105" t="n">
-        <v>6943661</v>
+        <v>6943740</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12644,7 +12658,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121174736</v>
+        <v>121174716</v>
       </c>
       <c r="B107" t="n">
         <v>98098</v>
@@ -12696,10 +12710,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491093</v>
+        <v>491104</v>
       </c>
       <c r="R107" t="n">
-        <v>6943580</v>
+        <v>6943581</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12759,7 +12773,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121175096</v>
+        <v>121173047</v>
       </c>
       <c r="B108" t="n">
         <v>98098</v>
@@ -12794,7 +12808,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -12807,14 +12821,14 @@
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor -Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491249</v>
+        <v>491069</v>
       </c>
       <c r="R108" t="n">
-        <v>6943270</v>
+        <v>6943744</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12874,7 +12888,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121174681</v>
+        <v>121173118</v>
       </c>
       <c r="B109" t="n">
         <v>98098</v>
@@ -12909,7 +12923,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -12926,10 +12940,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491091</v>
+        <v>491374</v>
       </c>
       <c r="R109" t="n">
-        <v>6943656</v>
+        <v>6943172</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12989,10 +13003,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121173042</v>
+        <v>121173066</v>
       </c>
       <c r="B110" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13001,39 +13015,30 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13041,10 +13046,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491060</v>
+        <v>491079</v>
       </c>
       <c r="R110" t="n">
-        <v>6943757</v>
+        <v>6943707</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13219,10 +13224,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121174660</v>
+        <v>121173075</v>
       </c>
       <c r="B112" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13231,39 +13236,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13271,10 +13267,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>491081</v>
+        <v>491094</v>
       </c>
       <c r="R112" t="n">
-        <v>6943657</v>
+        <v>6943719</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13334,7 +13330,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121174703</v>
+        <v>121173042</v>
       </c>
       <c r="B113" t="n">
         <v>98098</v>
@@ -13386,10 +13382,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>491096</v>
+        <v>491060</v>
       </c>
       <c r="R113" t="n">
-        <v>6943583</v>
+        <v>6943757</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13449,7 +13445,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121175104</v>
+        <v>121175096</v>
       </c>
       <c r="B114" t="n">
         <v>98098</v>
@@ -13487,20 +13483,24 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor -Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>491240</v>
+        <v>491249</v>
       </c>
       <c r="R114" t="n">
-        <v>6943272</v>
+        <v>6943270</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13560,7 +13560,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121173054</v>
+        <v>121174670</v>
       </c>
       <c r="B115" t="n">
         <v>79688</v>
@@ -13603,10 +13603,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>491077</v>
+        <v>491078</v>
       </c>
       <c r="R115" t="n">
-        <v>6943749</v>
+        <v>6943661</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13666,10 +13666,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121174608</v>
+        <v>121173054</v>
       </c>
       <c r="B116" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13678,39 +13678,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -13718,10 +13709,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>491341</v>
+        <v>491077</v>
       </c>
       <c r="R116" t="n">
-        <v>6943167</v>
+        <v>6943749</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13781,10 +13772,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121173030</v>
+        <v>121174638</v>
       </c>
       <c r="B117" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13793,30 +13784,39 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13824,10 +13824,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>491061</v>
+        <v>491327</v>
       </c>
       <c r="R117" t="n">
-        <v>6943779</v>
+        <v>6943200</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AY137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13885,6 +13885,2271 @@
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>121543021</v>
+      </c>
+      <c r="B118" t="n">
+        <v>78345</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>490921</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6943724</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>121541432</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>491187</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6943591</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>121541688</v>
+      </c>
+      <c r="B120" t="n">
+        <v>82392</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>491221</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6943638</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>121541329</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79197</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>491215</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6943527</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121541418</v>
+      </c>
+      <c r="B122" t="n">
+        <v>82392</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>491191</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6943589</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121540990</v>
+      </c>
+      <c r="B123" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>491111</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6943502</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>121542897</v>
+      </c>
+      <c r="B124" t="n">
+        <v>74706</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>308</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>491325</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6943735</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>121540656</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>491058</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6943647</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>121542668</v>
+      </c>
+      <c r="B126" t="n">
+        <v>56567</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>491339</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6943741</v>
+      </c>
+      <c r="S126" t="n">
+        <v>20</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>121541493</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>491173</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6943600</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>121540870</v>
+      </c>
+      <c r="B128" t="n">
+        <v>79197</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>491131</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6943593</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>121541195</v>
+      </c>
+      <c r="B129" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>491317</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6943408</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>121541303</v>
+      </c>
+      <c r="B130" t="n">
+        <v>78345</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>491256</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6943499</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>121541599</v>
+      </c>
+      <c r="B131" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>491226</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6943609</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>121540892</v>
+      </c>
+      <c r="B132" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>491148</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6943542</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>121540625</v>
+      </c>
+      <c r="B133" t="n">
+        <v>79197</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>491024</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6943620</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>121542839</v>
+      </c>
+      <c r="B134" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>491388</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6943720</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>121541348</v>
+      </c>
+      <c r="B135" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>491203</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6943563</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>121542288</v>
+      </c>
+      <c r="B136" t="n">
+        <v>56567</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>491296</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6943697</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>121542322</v>
+      </c>
+      <c r="B137" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>491303</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6943695</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -10415,7 +10415,7 @@
         <v>121175104</v>
       </c>
       <c r="B87" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10523,10 +10523,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121173058</v>
+        <v>121174691</v>
       </c>
       <c r="B88" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10535,30 +10535,39 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10566,10 +10575,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491060</v>
+        <v>491088</v>
       </c>
       <c r="R88" t="n">
-        <v>6943711</v>
+        <v>6943643</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10629,10 +10638,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121173030</v>
+        <v>121174619</v>
       </c>
       <c r="B89" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10641,30 +10650,39 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10672,10 +10690,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491061</v>
+        <v>491336</v>
       </c>
       <c r="R89" t="n">
-        <v>6943779</v>
+        <v>6943200</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10735,10 +10753,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121174651</v>
+        <v>121173118</v>
       </c>
       <c r="B90" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10770,7 +10788,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10787,10 +10805,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491092</v>
+        <v>491374</v>
       </c>
       <c r="R90" t="n">
-        <v>6943657</v>
+        <v>6943172</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10850,10 +10868,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121173037</v>
+        <v>121174660</v>
       </c>
       <c r="B91" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10862,30 +10880,39 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10893,10 +10920,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491068</v>
+        <v>491081</v>
       </c>
       <c r="R91" t="n">
-        <v>6943782</v>
+        <v>6943657</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10956,10 +10983,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121174736</v>
+        <v>121173088</v>
       </c>
       <c r="B92" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10968,39 +10995,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11008,10 +11026,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491093</v>
+        <v>491154</v>
       </c>
       <c r="R92" t="n">
-        <v>6943580</v>
+        <v>6943740</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11071,10 +11089,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121174660</v>
+        <v>121174644</v>
       </c>
       <c r="B93" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11106,7 +11124,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11123,10 +11141,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491081</v>
+        <v>491320</v>
       </c>
       <c r="R93" t="n">
-        <v>6943657</v>
+        <v>6943222</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11186,10 +11204,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121173022</v>
+        <v>121174716</v>
       </c>
       <c r="B94" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11198,30 +11216,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11229,10 +11256,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491045</v>
+        <v>491104</v>
       </c>
       <c r="R94" t="n">
-        <v>6943777</v>
+        <v>6943581</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11292,10 +11319,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121174619</v>
+        <v>121173066</v>
       </c>
       <c r="B95" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11304,39 +11331,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11344,10 +11362,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491336</v>
+        <v>491079</v>
       </c>
       <c r="R95" t="n">
-        <v>6943200</v>
+        <v>6943707</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11407,10 +11425,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121174710</v>
+        <v>121174703</v>
       </c>
       <c r="B96" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11442,7 +11460,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11459,10 +11477,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491099</v>
+        <v>491096</v>
       </c>
       <c r="R96" t="n">
-        <v>6943598</v>
+        <v>6943583</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11522,10 +11540,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121173006</v>
+        <v>121173022</v>
       </c>
       <c r="B97" t="n">
-        <v>56566</v>
+        <v>79689</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11534,39 +11552,30 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11574,10 +11583,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491047</v>
+        <v>491045</v>
       </c>
       <c r="R97" t="n">
-        <v>6943785</v>
+        <v>6943777</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11618,6 +11627,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11636,10 +11646,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121172997</v>
+        <v>121174670</v>
       </c>
       <c r="B98" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11679,10 +11689,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491043</v>
+        <v>491078</v>
       </c>
       <c r="R98" t="n">
-        <v>6943791</v>
+        <v>6943661</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11715,11 +11725,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11747,10 +11752,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121174681</v>
+        <v>121174736</v>
       </c>
       <c r="B99" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11782,7 +11787,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11799,10 +11804,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491091</v>
+        <v>491093</v>
       </c>
       <c r="R99" t="n">
-        <v>6943656</v>
+        <v>6943580</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11862,10 +11867,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121174642</v>
+        <v>121174681</v>
       </c>
       <c r="B100" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11910,14 +11915,14 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stor-lravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491319</v>
+        <v>491091</v>
       </c>
       <c r="R100" t="n">
-        <v>6943212</v>
+        <v>6943656</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11977,10 +11982,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121173101</v>
+        <v>121173054</v>
       </c>
       <c r="B101" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11989,39 +11994,30 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -12029,10 +12025,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491378</v>
+        <v>491077</v>
       </c>
       <c r="R101" t="n">
-        <v>6943184</v>
+        <v>6943749</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12092,10 +12088,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121174608</v>
+        <v>121172997</v>
       </c>
       <c r="B102" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12104,39 +12100,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12144,10 +12131,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491341</v>
+        <v>491043</v>
       </c>
       <c r="R102" t="n">
-        <v>6943167</v>
+        <v>6943791</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12180,6 +12167,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12207,10 +12199,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121174703</v>
+        <v>121175096</v>
       </c>
       <c r="B103" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12255,14 +12247,14 @@
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor -Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491096</v>
+        <v>491249</v>
       </c>
       <c r="R103" t="n">
-        <v>6943583</v>
+        <v>6943270</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12325,7 +12317,7 @@
         <v>121174973</v>
       </c>
       <c r="B104" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12437,10 +12429,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121173088</v>
+        <v>121173030</v>
       </c>
       <c r="B105" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12480,10 +12472,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491154</v>
+        <v>491061</v>
       </c>
       <c r="R105" t="n">
-        <v>6943740</v>
+        <v>6943779</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12543,10 +12535,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121174644</v>
+        <v>121173101</v>
       </c>
       <c r="B106" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12578,7 +12570,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12595,10 +12587,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491320</v>
+        <v>491378</v>
       </c>
       <c r="R106" t="n">
-        <v>6943222</v>
+        <v>6943184</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12658,10 +12650,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121174716</v>
+        <v>121173006</v>
       </c>
       <c r="B107" t="n">
-        <v>98098</v>
+        <v>56567</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12670,39 +12662,39 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -12710,10 +12702,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491104</v>
+        <v>491047</v>
       </c>
       <c r="R107" t="n">
-        <v>6943581</v>
+        <v>6943785</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12754,7 +12746,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12773,10 +12764,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121173047</v>
+        <v>121173037</v>
       </c>
       <c r="B108" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12785,39 +12776,30 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -12825,10 +12807,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491069</v>
+        <v>491068</v>
       </c>
       <c r="R108" t="n">
-        <v>6943744</v>
+        <v>6943782</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12888,10 +12870,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121173118</v>
+        <v>121174642</v>
       </c>
       <c r="B109" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12923,7 +12905,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -12936,14 +12918,14 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor-lravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491374</v>
+        <v>491319</v>
       </c>
       <c r="R109" t="n">
-        <v>6943172</v>
+        <v>6943212</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13003,10 +12985,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121173066</v>
+        <v>121174651</v>
       </c>
       <c r="B110" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13015,30 +12997,39 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13046,10 +13037,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491079</v>
+        <v>491092</v>
       </c>
       <c r="R110" t="n">
-        <v>6943707</v>
+        <v>6943657</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13109,10 +13100,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121174691</v>
+        <v>121173042</v>
       </c>
       <c r="B111" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13144,7 +13135,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13161,10 +13152,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>491088</v>
+        <v>491060</v>
       </c>
       <c r="R111" t="n">
-        <v>6943643</v>
+        <v>6943757</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13224,10 +13215,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121173075</v>
+        <v>121173047</v>
       </c>
       <c r="B112" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13236,30 +13227,39 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13267,10 +13267,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>491094</v>
+        <v>491069</v>
       </c>
       <c r="R112" t="n">
-        <v>6943719</v>
+        <v>6943744</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13330,10 +13330,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121173042</v>
+        <v>121173058</v>
       </c>
       <c r="B113" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13342,39 +13342,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -13385,7 +13376,7 @@
         <v>491060</v>
       </c>
       <c r="R113" t="n">
-        <v>6943757</v>
+        <v>6943711</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13445,10 +13436,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121175096</v>
+        <v>121173075</v>
       </c>
       <c r="B114" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13457,50 +13448,41 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stor -Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>491249</v>
+        <v>491094</v>
       </c>
       <c r="R114" t="n">
-        <v>6943270</v>
+        <v>6943719</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13560,10 +13542,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121174670</v>
+        <v>121174710</v>
       </c>
       <c r="B115" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13572,30 +13554,39 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -13603,10 +13594,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>491078</v>
+        <v>491099</v>
       </c>
       <c r="R115" t="n">
-        <v>6943661</v>
+        <v>6943598</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13666,10 +13657,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121173054</v>
+        <v>121174638</v>
       </c>
       <c r="B116" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13678,30 +13669,39 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -13709,10 +13709,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>491077</v>
+        <v>491327</v>
       </c>
       <c r="R116" t="n">
-        <v>6943749</v>
+        <v>6943200</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121174638</v>
+        <v>121174608</v>
       </c>
       <c r="B117" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13824,10 +13824,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>491327</v>
+        <v>491341</v>
       </c>
       <c r="R117" t="n">
-        <v>6943200</v>
+        <v>6943167</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13887,10 +13887,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121543021</v>
+        <v>121541688</v>
       </c>
       <c r="B118" t="n">
-        <v>78345</v>
+        <v>82392</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13903,34 +13903,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490921</v>
+        <v>491221</v>
       </c>
       <c r="R118" t="n">
-        <v>6943724</v>
+        <v>6943638</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13999,10 +13999,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121541432</v>
+        <v>121540892</v>
       </c>
       <c r="B119" t="n">
-        <v>79690</v>
+        <v>78608</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14015,21 +14015,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14039,10 +14039,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>491187</v>
+        <v>491148</v>
       </c>
       <c r="R119" t="n">
-        <v>6943591</v>
+        <v>6943542</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14111,10 +14111,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121541688</v>
+        <v>121540656</v>
       </c>
       <c r="B120" t="n">
-        <v>82392</v>
+        <v>79689</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14127,34 +14127,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>491221</v>
+        <v>491058</v>
       </c>
       <c r="R120" t="n">
-        <v>6943638</v>
+        <v>6943647</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14223,10 +14223,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121541329</v>
+        <v>121541303</v>
       </c>
       <c r="B121" t="n">
-        <v>79197</v>
+        <v>78345</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14239,34 +14239,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>491215</v>
+        <v>491256</v>
       </c>
       <c r="R121" t="n">
-        <v>6943527</v>
+        <v>6943499</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14298,7 +14298,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14335,10 +14335,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121541418</v>
+        <v>121542897</v>
       </c>
       <c r="B122" t="n">
-        <v>82392</v>
+        <v>74706</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14351,34 +14351,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>491191</v>
+        <v>491325</v>
       </c>
       <c r="R122" t="n">
-        <v>6943589</v>
+        <v>6943735</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14410,7 +14410,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14447,7 +14447,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121540990</v>
+        <v>121542322</v>
       </c>
       <c r="B123" t="n">
         <v>78608</v>
@@ -14483,14 +14483,14 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>491111</v>
+        <v>491303</v>
       </c>
       <c r="R123" t="n">
-        <v>6943502</v>
+        <v>6943695</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14522,7 +14522,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14559,10 +14559,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121542897</v>
+        <v>121541195</v>
       </c>
       <c r="B124" t="n">
-        <v>74706</v>
+        <v>78608</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14575,21 +14575,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14599,10 +14599,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>491325</v>
+        <v>491317</v>
       </c>
       <c r="R124" t="n">
-        <v>6943735</v>
+        <v>6943408</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14671,10 +14671,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121540656</v>
+        <v>121542839</v>
       </c>
       <c r="B125" t="n">
-        <v>79689</v>
+        <v>78608</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14687,34 +14687,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>491058</v>
+        <v>491388</v>
       </c>
       <c r="R125" t="n">
-        <v>6943647</v>
+        <v>6943720</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14783,10 +14783,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121542668</v>
+        <v>121541432</v>
       </c>
       <c r="B126" t="n">
-        <v>56567</v>
+        <v>79690</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14795,56 +14795,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>491339</v>
+        <v>491187</v>
       </c>
       <c r="R126" t="n">
-        <v>6943741</v>
+        <v>6943591</v>
       </c>
       <c r="S126" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14873,7 +14858,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14883,7 +14868,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14910,10 +14895,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121541493</v>
+        <v>121542668</v>
       </c>
       <c r="B127" t="n">
-        <v>79689</v>
+        <v>56567</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14922,41 +14907,56 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>491173</v>
+        <v>491339</v>
       </c>
       <c r="R127" t="n">
-        <v>6943600</v>
+        <v>6943741</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15022,10 +15022,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121540870</v>
+        <v>121542288</v>
       </c>
       <c r="B128" t="n">
-        <v>79197</v>
+        <v>56567</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15034,38 +15034,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>491131</v>
+        <v>491296</v>
       </c>
       <c r="R128" t="n">
-        <v>6943593</v>
+        <v>6943697</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15097,7 +15102,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15107,12 +15112,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15139,10 +15139,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121541195</v>
+        <v>121541418</v>
       </c>
       <c r="B129" t="n">
-        <v>78608</v>
+        <v>82392</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15155,34 +15155,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>491317</v>
+        <v>491191</v>
       </c>
       <c r="R129" t="n">
-        <v>6943408</v>
+        <v>6943589</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15214,7 +15214,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15251,10 +15251,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121541303</v>
+        <v>121541329</v>
       </c>
       <c r="B130" t="n">
-        <v>78345</v>
+        <v>79197</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15267,34 +15267,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>491256</v>
+        <v>491215</v>
       </c>
       <c r="R130" t="n">
-        <v>6943499</v>
+        <v>6943527</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15363,10 +15363,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121541599</v>
+        <v>121543021</v>
       </c>
       <c r="B131" t="n">
-        <v>78608</v>
+        <v>78345</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15379,34 +15379,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>491226</v>
+        <v>490921</v>
       </c>
       <c r="R131" t="n">
-        <v>6943609</v>
+        <v>6943724</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15475,7 +15475,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121540892</v>
+        <v>121541599</v>
       </c>
       <c r="B132" t="n">
         <v>78608</v>
@@ -15511,14 +15511,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491148</v>
+        <v>491226</v>
       </c>
       <c r="R132" t="n">
-        <v>6943542</v>
+        <v>6943609</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15699,10 +15699,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121542839</v>
+        <v>121541493</v>
       </c>
       <c r="B134" t="n">
-        <v>78608</v>
+        <v>79689</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15715,34 +15715,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>491388</v>
+        <v>491173</v>
       </c>
       <c r="R134" t="n">
-        <v>6943720</v>
+        <v>6943600</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15923,10 +15923,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121542288</v>
+        <v>121540990</v>
       </c>
       <c r="B136" t="n">
-        <v>56567</v>
+        <v>78608</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15935,43 +15935,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>491296</v>
+        <v>491111</v>
       </c>
       <c r="R136" t="n">
-        <v>6943697</v>
+        <v>6943502</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16003,7 +15998,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16013,7 +16008,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16040,10 +16035,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121542322</v>
+        <v>121540870</v>
       </c>
       <c r="B137" t="n">
-        <v>78608</v>
+        <v>79197</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16056,34 +16051,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>491303</v>
+        <v>491131</v>
       </c>
       <c r="R137" t="n">
-        <v>6943695</v>
+        <v>6943593</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16115,7 +16110,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16125,7 +16120,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
         </is>
       </c>
       <c r="AD137" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -14559,7 +14559,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121541195</v>
+        <v>121542839</v>
       </c>
       <c r="B124" t="n">
         <v>78608</v>
@@ -14599,10 +14599,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>491317</v>
+        <v>491388</v>
       </c>
       <c r="R124" t="n">
-        <v>6943408</v>
+        <v>6943720</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14671,7 +14671,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121542839</v>
+        <v>121541195</v>
       </c>
       <c r="B125" t="n">
         <v>78608</v>
@@ -14711,10 +14711,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>491388</v>
+        <v>491317</v>
       </c>
       <c r="R125" t="n">
-        <v>6943720</v>
+        <v>6943408</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD125" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -13887,10 +13887,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121541688</v>
+        <v>121540892</v>
       </c>
       <c r="B118" t="n">
-        <v>82392</v>
+        <v>78609</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13903,34 +13903,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>491221</v>
+        <v>491148</v>
       </c>
       <c r="R118" t="n">
-        <v>6943638</v>
+        <v>6943542</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13999,10 +13999,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121540892</v>
+        <v>121542897</v>
       </c>
       <c r="B119" t="n">
-        <v>78608</v>
+        <v>74707</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14015,34 +14015,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>491148</v>
+        <v>491325</v>
       </c>
       <c r="R119" t="n">
-        <v>6943542</v>
+        <v>6943735</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14111,10 +14111,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121540656</v>
+        <v>121541329</v>
       </c>
       <c r="B120" t="n">
-        <v>79689</v>
+        <v>79198</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14127,21 +14127,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14151,10 +14151,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>491058</v>
+        <v>491215</v>
       </c>
       <c r="R120" t="n">
-        <v>6943647</v>
+        <v>6943527</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14223,10 +14223,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121541303</v>
+        <v>121542288</v>
       </c>
       <c r="B121" t="n">
-        <v>78345</v>
+        <v>56568</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14235,38 +14235,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>491256</v>
+        <v>491296</v>
       </c>
       <c r="R121" t="n">
-        <v>6943499</v>
+        <v>6943697</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14298,7 +14303,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14308,7 +14313,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14335,10 +14340,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121542897</v>
+        <v>121540990</v>
       </c>
       <c r="B122" t="n">
-        <v>74706</v>
+        <v>78609</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14351,34 +14356,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>491325</v>
+        <v>491111</v>
       </c>
       <c r="R122" t="n">
-        <v>6943735</v>
+        <v>6943502</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14410,7 +14415,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14420,7 +14425,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14447,10 +14452,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121542322</v>
+        <v>121540656</v>
       </c>
       <c r="B123" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14463,34 +14468,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>491303</v>
+        <v>491058</v>
       </c>
       <c r="R123" t="n">
-        <v>6943695</v>
+        <v>6943647</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14522,7 +14527,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14532,7 +14537,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14559,10 +14564,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121542839</v>
+        <v>121542322</v>
       </c>
       <c r="B124" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14599,10 +14604,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>491388</v>
+        <v>491303</v>
       </c>
       <c r="R124" t="n">
-        <v>6943720</v>
+        <v>6943695</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14634,7 +14639,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14644,7 +14649,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14671,10 +14676,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121541195</v>
+        <v>121541599</v>
       </c>
       <c r="B125" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14711,10 +14716,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>491317</v>
+        <v>491226</v>
       </c>
       <c r="R125" t="n">
-        <v>6943408</v>
+        <v>6943609</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14746,7 +14751,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14756,7 +14761,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14783,10 +14788,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121541432</v>
+        <v>121540870</v>
       </c>
       <c r="B126" t="n">
-        <v>79690</v>
+        <v>79198</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14799,21 +14804,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14823,10 +14828,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>491187</v>
+        <v>491131</v>
       </c>
       <c r="R126" t="n">
-        <v>6943591</v>
+        <v>6943593</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14858,7 +14863,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14868,7 +14873,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14895,10 +14905,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121542668</v>
+        <v>121541303</v>
       </c>
       <c r="B127" t="n">
-        <v>56567</v>
+        <v>78346</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14907,56 +14917,41 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>491339</v>
+        <v>491256</v>
       </c>
       <c r="R127" t="n">
-        <v>6943741</v>
+        <v>6943499</v>
       </c>
       <c r="S127" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14985,7 +14980,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14995,7 +14990,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15022,10 +15017,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121542288</v>
+        <v>121543021</v>
       </c>
       <c r="B128" t="n">
-        <v>56567</v>
+        <v>78346</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15034,43 +15029,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>491296</v>
+        <v>490921</v>
       </c>
       <c r="R128" t="n">
-        <v>6943697</v>
+        <v>6943724</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15102,7 +15092,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15112,7 +15102,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15139,10 +15129,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121541418</v>
+        <v>121541493</v>
       </c>
       <c r="B129" t="n">
-        <v>82392</v>
+        <v>79690</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15155,21 +15145,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15179,10 +15169,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>491191</v>
+        <v>491173</v>
       </c>
       <c r="R129" t="n">
-        <v>6943589</v>
+        <v>6943600</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15214,7 +15204,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15224,7 +15214,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15251,10 +15241,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121541329</v>
+        <v>121541432</v>
       </c>
       <c r="B130" t="n">
-        <v>79197</v>
+        <v>79691</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15267,21 +15257,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15291,10 +15281,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>491215</v>
+        <v>491187</v>
       </c>
       <c r="R130" t="n">
-        <v>6943527</v>
+        <v>6943591</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15326,7 +15316,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15336,7 +15326,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15363,10 +15353,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121543021</v>
+        <v>121541418</v>
       </c>
       <c r="B131" t="n">
-        <v>78345</v>
+        <v>82393</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15379,34 +15369,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>490921</v>
+        <v>491191</v>
       </c>
       <c r="R131" t="n">
-        <v>6943724</v>
+        <v>6943589</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15438,7 +15428,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15448,7 +15438,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15475,10 +15465,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121541599</v>
+        <v>121541195</v>
       </c>
       <c r="B132" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15515,10 +15505,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491226</v>
+        <v>491317</v>
       </c>
       <c r="R132" t="n">
-        <v>6943609</v>
+        <v>6943408</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15550,7 +15540,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15560,7 +15550,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15587,10 +15577,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121540625</v>
+        <v>121541348</v>
       </c>
       <c r="B133" t="n">
-        <v>79197</v>
+        <v>78609</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15603,21 +15593,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15627,10 +15617,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491024</v>
+        <v>491203</v>
       </c>
       <c r="R133" t="n">
-        <v>6943620</v>
+        <v>6943563</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15662,7 +15652,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15672,7 +15662,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15699,10 +15689,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121541493</v>
+        <v>121540625</v>
       </c>
       <c r="B134" t="n">
-        <v>79689</v>
+        <v>79198</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15715,21 +15705,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15739,10 +15729,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>491173</v>
+        <v>491024</v>
       </c>
       <c r="R134" t="n">
-        <v>6943600</v>
+        <v>6943620</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15774,7 +15764,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15784,7 +15774,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15811,10 +15801,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121541348</v>
+        <v>121541688</v>
       </c>
       <c r="B135" t="n">
-        <v>78608</v>
+        <v>82393</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15827,34 +15817,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491203</v>
+        <v>491221</v>
       </c>
       <c r="R135" t="n">
-        <v>6943563</v>
+        <v>6943638</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15886,7 +15876,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15896,7 +15886,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15923,10 +15913,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121540990</v>
+        <v>121542668</v>
       </c>
       <c r="B136" t="n">
-        <v>78608</v>
+        <v>56568</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15935,41 +15925,56 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>491111</v>
+        <v>491339</v>
       </c>
       <c r="R136" t="n">
-        <v>6943502</v>
+        <v>6943741</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15998,7 +16003,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16008,7 +16013,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16035,10 +16040,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121540870</v>
+        <v>121542839</v>
       </c>
       <c r="B137" t="n">
-        <v>79197</v>
+        <v>78609</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16051,34 +16056,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>491131</v>
+        <v>491388</v>
       </c>
       <c r="R137" t="n">
-        <v>6943593</v>
+        <v>6943720</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16110,7 +16115,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16120,12 +16125,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD137" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -13887,10 +13887,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121540892</v>
+        <v>121541329</v>
       </c>
       <c r="B118" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13903,21 +13903,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13927,10 +13927,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>491148</v>
+        <v>491215</v>
       </c>
       <c r="R118" t="n">
-        <v>6943542</v>
+        <v>6943527</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13999,10 +13999,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121542897</v>
+        <v>121542322</v>
       </c>
       <c r="B119" t="n">
-        <v>74707</v>
+        <v>78609</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14015,21 +14015,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14039,10 +14039,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>491325</v>
+        <v>491303</v>
       </c>
       <c r="R119" t="n">
-        <v>6943735</v>
+        <v>6943695</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14111,10 +14111,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121541329</v>
+        <v>121542668</v>
       </c>
       <c r="B120" t="n">
-        <v>79198</v>
+        <v>56568</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14123,41 +14123,56 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>491215</v>
+        <v>491339</v>
       </c>
       <c r="R120" t="n">
-        <v>6943527</v>
+        <v>6943741</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14186,7 +14201,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14196,7 +14211,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14223,10 +14238,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121542288</v>
+        <v>121543021</v>
       </c>
       <c r="B121" t="n">
-        <v>56568</v>
+        <v>78346</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14235,43 +14250,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>491296</v>
+        <v>490921</v>
       </c>
       <c r="R121" t="n">
-        <v>6943697</v>
+        <v>6943724</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14303,7 +14313,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14313,7 +14323,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14340,7 +14350,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121540990</v>
+        <v>121541348</v>
       </c>
       <c r="B122" t="n">
         <v>78609</v>
@@ -14380,10 +14390,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>491111</v>
+        <v>491203</v>
       </c>
       <c r="R122" t="n">
-        <v>6943502</v>
+        <v>6943563</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14415,7 +14425,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14425,7 +14435,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14452,10 +14462,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121540656</v>
+        <v>121541303</v>
       </c>
       <c r="B123" t="n">
-        <v>79690</v>
+        <v>78346</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14468,34 +14478,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>491058</v>
+        <v>491256</v>
       </c>
       <c r="R123" t="n">
-        <v>6943647</v>
+        <v>6943499</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14527,7 +14537,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14537,7 +14547,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14564,10 +14574,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121542322</v>
+        <v>121540625</v>
       </c>
       <c r="B124" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14580,34 +14590,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>491303</v>
+        <v>491024</v>
       </c>
       <c r="R124" t="n">
-        <v>6943695</v>
+        <v>6943620</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14639,7 +14649,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14649,7 +14659,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14676,7 +14686,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121541599</v>
+        <v>121540892</v>
       </c>
       <c r="B125" t="n">
         <v>78609</v>
@@ -14712,14 +14722,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>491226</v>
+        <v>491148</v>
       </c>
       <c r="R125" t="n">
-        <v>6943609</v>
+        <v>6943542</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14751,7 +14761,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14761,7 +14771,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14788,10 +14798,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121540870</v>
+        <v>121541599</v>
       </c>
       <c r="B126" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14804,34 +14814,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>491131</v>
+        <v>491226</v>
       </c>
       <c r="R126" t="n">
-        <v>6943593</v>
+        <v>6943609</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14863,7 +14873,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14873,12 +14883,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14905,10 +14910,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121541303</v>
+        <v>121541688</v>
       </c>
       <c r="B127" t="n">
-        <v>78346</v>
+        <v>82393</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14921,21 +14926,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14945,10 +14950,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>491256</v>
+        <v>491221</v>
       </c>
       <c r="R127" t="n">
-        <v>6943499</v>
+        <v>6943638</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14980,7 +14985,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14990,7 +14995,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15017,10 +15022,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121543021</v>
+        <v>121540870</v>
       </c>
       <c r="B128" t="n">
-        <v>78346</v>
+        <v>79198</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15033,34 +15038,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>490921</v>
+        <v>491131</v>
       </c>
       <c r="R128" t="n">
-        <v>6943724</v>
+        <v>6943593</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15092,7 +15097,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15102,7 +15107,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15129,7 +15139,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121541493</v>
+        <v>121540656</v>
       </c>
       <c r="B129" t="n">
         <v>79690</v>
@@ -15169,10 +15179,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>491173</v>
+        <v>491058</v>
       </c>
       <c r="R129" t="n">
-        <v>6943600</v>
+        <v>6943647</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15204,7 +15214,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15214,7 +15224,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15241,10 +15251,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121541432</v>
+        <v>121542839</v>
       </c>
       <c r="B130" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15257,34 +15267,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>491187</v>
+        <v>491388</v>
       </c>
       <c r="R130" t="n">
-        <v>6943591</v>
+        <v>6943720</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15316,7 +15326,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15326,7 +15336,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15353,10 +15363,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121541418</v>
+        <v>121542288</v>
       </c>
       <c r="B131" t="n">
-        <v>82393</v>
+        <v>56568</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15365,38 +15375,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>491191</v>
+        <v>491296</v>
       </c>
       <c r="R131" t="n">
-        <v>6943589</v>
+        <v>6943697</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15428,7 +15443,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15438,7 +15453,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15465,10 +15480,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121541195</v>
+        <v>121541493</v>
       </c>
       <c r="B132" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15481,34 +15496,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491317</v>
+        <v>491173</v>
       </c>
       <c r="R132" t="n">
-        <v>6943408</v>
+        <v>6943600</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15540,7 +15555,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15550,7 +15565,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15577,7 +15592,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121541348</v>
+        <v>121540990</v>
       </c>
       <c r="B133" t="n">
         <v>78609</v>
@@ -15617,10 +15632,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491203</v>
+        <v>491111</v>
       </c>
       <c r="R133" t="n">
-        <v>6943563</v>
+        <v>6943502</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15652,7 +15667,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15662,7 +15677,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15689,10 +15704,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121540625</v>
+        <v>121541195</v>
       </c>
       <c r="B134" t="n">
-        <v>79198</v>
+        <v>78609</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15705,34 +15720,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>491024</v>
+        <v>491317</v>
       </c>
       <c r="R134" t="n">
-        <v>6943620</v>
+        <v>6943408</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15764,7 +15779,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15774,7 +15789,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15801,10 +15816,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121541688</v>
+        <v>121542897</v>
       </c>
       <c r="B135" t="n">
-        <v>82393</v>
+        <v>74707</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15817,21 +15832,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15841,10 +15856,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491221</v>
+        <v>491325</v>
       </c>
       <c r="R135" t="n">
-        <v>6943638</v>
+        <v>6943735</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15876,7 +15891,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15886,7 +15901,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15913,10 +15928,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121542668</v>
+        <v>121541418</v>
       </c>
       <c r="B136" t="n">
-        <v>56568</v>
+        <v>82393</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15925,56 +15940,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>491339</v>
+        <v>491191</v>
       </c>
       <c r="R136" t="n">
-        <v>6943741</v>
+        <v>6943589</v>
       </c>
       <c r="S136" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16040,10 +16040,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121542839</v>
+        <v>121541432</v>
       </c>
       <c r="B137" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16056,34 +16056,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>491388</v>
+        <v>491187</v>
       </c>
       <c r="R137" t="n">
-        <v>6943720</v>
+        <v>6943591</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD137" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -13887,10 +13887,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121541329</v>
+        <v>121541688</v>
       </c>
       <c r="B118" t="n">
-        <v>79198</v>
+        <v>82393</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13903,34 +13903,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>491215</v>
+        <v>491221</v>
       </c>
       <c r="R118" t="n">
-        <v>6943527</v>
+        <v>6943638</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13999,10 +13999,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121542322</v>
+        <v>121541493</v>
       </c>
       <c r="B119" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14015,34 +14015,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>491303</v>
+        <v>491173</v>
       </c>
       <c r="R119" t="n">
-        <v>6943695</v>
+        <v>6943600</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14111,10 +14111,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121542668</v>
+        <v>121541418</v>
       </c>
       <c r="B120" t="n">
-        <v>56568</v>
+        <v>82393</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14123,56 +14123,41 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>491339</v>
+        <v>491191</v>
       </c>
       <c r="R120" t="n">
-        <v>6943741</v>
+        <v>6943589</v>
       </c>
       <c r="S120" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14201,7 +14186,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14211,7 +14196,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14238,10 +14223,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121543021</v>
+        <v>121542839</v>
       </c>
       <c r="B121" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14254,34 +14239,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490921</v>
+        <v>491388</v>
       </c>
       <c r="R121" t="n">
-        <v>6943724</v>
+        <v>6943720</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14313,7 +14298,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14323,7 +14308,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14350,10 +14335,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121541348</v>
+        <v>121540870</v>
       </c>
       <c r="B122" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14366,21 +14351,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14390,10 +14375,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>491203</v>
+        <v>491131</v>
       </c>
       <c r="R122" t="n">
-        <v>6943563</v>
+        <v>6943593</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14425,7 +14410,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14435,7 +14420,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14462,10 +14452,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121541303</v>
+        <v>121542897</v>
       </c>
       <c r="B123" t="n">
-        <v>78346</v>
+        <v>74707</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14478,21 +14468,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14502,10 +14492,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>491256</v>
+        <v>491325</v>
       </c>
       <c r="R123" t="n">
-        <v>6943499</v>
+        <v>6943735</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14537,7 +14527,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14547,7 +14537,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14574,10 +14564,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121540625</v>
+        <v>121543021</v>
       </c>
       <c r="B124" t="n">
-        <v>79198</v>
+        <v>78346</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14590,34 +14580,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>491024</v>
+        <v>490921</v>
       </c>
       <c r="R124" t="n">
-        <v>6943620</v>
+        <v>6943724</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14649,7 +14639,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14659,7 +14649,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14686,7 +14676,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121540892</v>
+        <v>121541348</v>
       </c>
       <c r="B125" t="n">
         <v>78609</v>
@@ -14726,10 +14716,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>491148</v>
+        <v>491203</v>
       </c>
       <c r="R125" t="n">
-        <v>6943542</v>
+        <v>6943563</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14761,7 +14751,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14771,7 +14761,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14798,10 +14788,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121541599</v>
+        <v>121540625</v>
       </c>
       <c r="B126" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14814,34 +14804,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>491226</v>
+        <v>491024</v>
       </c>
       <c r="R126" t="n">
-        <v>6943609</v>
+        <v>6943620</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14873,7 +14863,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14883,7 +14873,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14910,10 +14900,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121541688</v>
+        <v>121541432</v>
       </c>
       <c r="B127" t="n">
-        <v>82393</v>
+        <v>79691</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14926,34 +14916,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>491221</v>
+        <v>491187</v>
       </c>
       <c r="R127" t="n">
-        <v>6943638</v>
+        <v>6943591</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14985,7 +14975,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14995,7 +14985,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15022,10 +15012,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121540870</v>
+        <v>121542668</v>
       </c>
       <c r="B128" t="n">
-        <v>79198</v>
+        <v>56568</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15034,41 +15024,56 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>491131</v>
+        <v>491339</v>
       </c>
       <c r="R128" t="n">
-        <v>6943593</v>
+        <v>6943741</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15097,7 +15102,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15107,12 +15112,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15139,10 +15139,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121540656</v>
+        <v>121540892</v>
       </c>
       <c r="B129" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15155,21 +15155,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15179,10 +15179,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>491058</v>
+        <v>491148</v>
       </c>
       <c r="R129" t="n">
-        <v>6943647</v>
+        <v>6943542</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15214,7 +15214,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15251,7 +15251,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121542839</v>
+        <v>121540990</v>
       </c>
       <c r="B130" t="n">
         <v>78609</v>
@@ -15287,14 +15287,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>491388</v>
+        <v>491111</v>
       </c>
       <c r="R130" t="n">
-        <v>6943720</v>
+        <v>6943502</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15480,10 +15480,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121541493</v>
+        <v>121541329</v>
       </c>
       <c r="B132" t="n">
-        <v>79690</v>
+        <v>79198</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15496,21 +15496,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491173</v>
+        <v>491215</v>
       </c>
       <c r="R132" t="n">
-        <v>6943600</v>
+        <v>6943527</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15592,7 +15592,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121540990</v>
+        <v>121542322</v>
       </c>
       <c r="B133" t="n">
         <v>78609</v>
@@ -15628,14 +15628,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491111</v>
+        <v>491303</v>
       </c>
       <c r="R133" t="n">
-        <v>6943502</v>
+        <v>6943695</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15704,7 +15704,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121541195</v>
+        <v>121541599</v>
       </c>
       <c r="B134" t="n">
         <v>78609</v>
@@ -15744,10 +15744,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>491317</v>
+        <v>491226</v>
       </c>
       <c r="R134" t="n">
-        <v>6943408</v>
+        <v>6943609</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15789,7 +15789,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15816,10 +15816,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121542897</v>
+        <v>121541303</v>
       </c>
       <c r="B135" t="n">
-        <v>74707</v>
+        <v>78346</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15832,21 +15832,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15856,10 +15856,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491325</v>
+        <v>491256</v>
       </c>
       <c r="R135" t="n">
-        <v>6943735</v>
+        <v>6943499</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15928,10 +15928,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121541418</v>
+        <v>121540656</v>
       </c>
       <c r="B136" t="n">
-        <v>82393</v>
+        <v>79690</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15944,21 +15944,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15968,10 +15968,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>491191</v>
+        <v>491058</v>
       </c>
       <c r="R136" t="n">
-        <v>6943589</v>
+        <v>6943647</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16040,10 +16040,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121541432</v>
+        <v>121541195</v>
       </c>
       <c r="B137" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16056,34 +16056,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>491187</v>
+        <v>491317</v>
       </c>
       <c r="R137" t="n">
-        <v>6943591</v>
+        <v>6943408</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD137" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -13887,10 +13887,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121541688</v>
+        <v>121542668</v>
       </c>
       <c r="B118" t="n">
-        <v>82393</v>
+        <v>56568</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13899,41 +13899,56 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>491221</v>
+        <v>491339</v>
       </c>
       <c r="R118" t="n">
-        <v>6943638</v>
+        <v>6943741</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13962,7 +13977,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13972,7 +13987,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13999,10 +14014,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121541493</v>
+        <v>121542897</v>
       </c>
       <c r="B119" t="n">
-        <v>79690</v>
+        <v>74707</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14015,34 +14030,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>491173</v>
+        <v>491325</v>
       </c>
       <c r="R119" t="n">
-        <v>6943600</v>
+        <v>6943735</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14074,7 +14089,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14084,7 +14099,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14111,10 +14126,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121541418</v>
+        <v>121542839</v>
       </c>
       <c r="B120" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14127,34 +14142,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>491191</v>
+        <v>491388</v>
       </c>
       <c r="R120" t="n">
-        <v>6943589</v>
+        <v>6943720</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14186,7 +14201,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14196,7 +14211,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14223,10 +14238,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121542839</v>
+        <v>121541432</v>
       </c>
       <c r="B121" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14239,34 +14254,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>491388</v>
+        <v>491187</v>
       </c>
       <c r="R121" t="n">
-        <v>6943720</v>
+        <v>6943591</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14298,7 +14313,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14308,7 +14323,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14335,10 +14350,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121540870</v>
+        <v>121541418</v>
       </c>
       <c r="B122" t="n">
-        <v>79198</v>
+        <v>82393</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14351,21 +14366,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14375,10 +14390,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>491131</v>
+        <v>491191</v>
       </c>
       <c r="R122" t="n">
-        <v>6943593</v>
+        <v>6943589</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14410,7 +14425,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14420,12 +14435,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14452,10 +14462,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121542897</v>
+        <v>121541329</v>
       </c>
       <c r="B123" t="n">
-        <v>74707</v>
+        <v>79198</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14468,34 +14478,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>308</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>491325</v>
+        <v>491215</v>
       </c>
       <c r="R123" t="n">
-        <v>6943735</v>
+        <v>6943527</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14527,7 +14537,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14537,7 +14547,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14564,10 +14574,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121543021</v>
+        <v>121541195</v>
       </c>
       <c r="B124" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14580,34 +14590,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490921</v>
+        <v>491317</v>
       </c>
       <c r="R124" t="n">
-        <v>6943724</v>
+        <v>6943408</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14639,7 +14649,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14649,7 +14659,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14676,7 +14686,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121541348</v>
+        <v>121540892</v>
       </c>
       <c r="B125" t="n">
         <v>78609</v>
@@ -14716,10 +14726,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>491203</v>
+        <v>491148</v>
       </c>
       <c r="R125" t="n">
-        <v>6943563</v>
+        <v>6943542</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14751,7 +14761,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14761,7 +14771,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14788,7 +14798,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121540625</v>
+        <v>121540870</v>
       </c>
       <c r="B126" t="n">
         <v>79198</v>
@@ -14828,10 +14838,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>491024</v>
+        <v>491131</v>
       </c>
       <c r="R126" t="n">
-        <v>6943620</v>
+        <v>6943593</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14863,7 +14873,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14873,7 +14883,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14900,10 +14915,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121541432</v>
+        <v>121541688</v>
       </c>
       <c r="B127" t="n">
-        <v>79691</v>
+        <v>82393</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14916,34 +14931,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>491187</v>
+        <v>491221</v>
       </c>
       <c r="R127" t="n">
-        <v>6943591</v>
+        <v>6943638</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14975,7 +14990,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14985,7 +15000,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15012,7 +15027,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121542668</v>
+        <v>121542288</v>
       </c>
       <c r="B128" t="n">
         <v>56568</v>
@@ -15046,19 +15061,9 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -15067,13 +15072,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>491339</v>
+        <v>491296</v>
       </c>
       <c r="R128" t="n">
-        <v>6943741</v>
+        <v>6943697</v>
       </c>
       <c r="S128" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15102,7 +15107,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15112,7 +15117,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15139,7 +15144,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121540892</v>
+        <v>121541348</v>
       </c>
       <c r="B129" t="n">
         <v>78609</v>
@@ -15179,10 +15184,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>491148</v>
+        <v>491203</v>
       </c>
       <c r="R129" t="n">
-        <v>6943542</v>
+        <v>6943563</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15214,7 +15219,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15224,7 +15229,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15363,10 +15368,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121542288</v>
+        <v>121540625</v>
       </c>
       <c r="B131" t="n">
-        <v>56568</v>
+        <v>79198</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15375,43 +15380,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>491296</v>
+        <v>491024</v>
       </c>
       <c r="R131" t="n">
-        <v>6943697</v>
+        <v>6943620</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15443,7 +15443,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15480,10 +15480,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121541329</v>
+        <v>121541303</v>
       </c>
       <c r="B132" t="n">
-        <v>79198</v>
+        <v>78346</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15496,34 +15496,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491215</v>
+        <v>491256</v>
       </c>
       <c r="R132" t="n">
-        <v>6943527</v>
+        <v>6943499</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15592,10 +15592,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121542322</v>
+        <v>121540656</v>
       </c>
       <c r="B133" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15608,34 +15608,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491303</v>
+        <v>491058</v>
       </c>
       <c r="R133" t="n">
-        <v>6943695</v>
+        <v>6943647</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15816,7 +15816,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121541303</v>
+        <v>121543021</v>
       </c>
       <c r="B135" t="n">
         <v>78346</v>
@@ -15852,14 +15852,14 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491256</v>
+        <v>490921</v>
       </c>
       <c r="R135" t="n">
-        <v>6943499</v>
+        <v>6943724</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15928,7 +15928,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121540656</v>
+        <v>121541493</v>
       </c>
       <c r="B136" t="n">
         <v>79690</v>
@@ -15968,10 +15968,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>491058</v>
+        <v>491173</v>
       </c>
       <c r="R136" t="n">
-        <v>6943647</v>
+        <v>6943600</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16040,7 +16040,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121541195</v>
+        <v>121542322</v>
       </c>
       <c r="B137" t="n">
         <v>78609</v>
@@ -16080,10 +16080,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>491317</v>
+        <v>491303</v>
       </c>
       <c r="R137" t="n">
-        <v>6943408</v>
+        <v>6943695</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD137" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY137"/>
+  <dimension ref="A1:AY139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14126,10 +14126,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121542839</v>
+        <v>121541432</v>
       </c>
       <c r="B120" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14142,34 +14142,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>491388</v>
+        <v>491187</v>
       </c>
       <c r="R120" t="n">
-        <v>6943720</v>
+        <v>6943591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14238,10 +14238,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121541432</v>
+        <v>121542839</v>
       </c>
       <c r="B121" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14254,34 +14254,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>491187</v>
+        <v>491388</v>
       </c>
       <c r="R121" t="n">
-        <v>6943591</v>
+        <v>6943720</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15592,10 +15592,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121540656</v>
+        <v>121543021</v>
       </c>
       <c r="B133" t="n">
-        <v>79690</v>
+        <v>78346</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15608,34 +15608,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491058</v>
+        <v>490921</v>
       </c>
       <c r="R133" t="n">
-        <v>6943647</v>
+        <v>6943724</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15816,10 +15816,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121543021</v>
+        <v>121540656</v>
       </c>
       <c r="B135" t="n">
-        <v>78346</v>
+        <v>79690</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15832,34 +15832,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>490921</v>
+        <v>491058</v>
       </c>
       <c r="R135" t="n">
-        <v>6943724</v>
+        <v>6943647</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16150,6 +16150,220 @@
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>121659358</v>
+      </c>
+      <c r="B138" t="n">
+        <v>55958</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>491021</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6943660</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>121659363</v>
+      </c>
+      <c r="B139" t="n">
+        <v>55958</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>491314</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6943736</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -14126,10 +14126,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121541432</v>
+        <v>121542839</v>
       </c>
       <c r="B120" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14142,34 +14142,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>491187</v>
+        <v>491388</v>
       </c>
       <c r="R120" t="n">
-        <v>6943591</v>
+        <v>6943720</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14238,10 +14238,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121542839</v>
+        <v>121541432</v>
       </c>
       <c r="B121" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14254,34 +14254,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>491388</v>
+        <v>491187</v>
       </c>
       <c r="R121" t="n">
-        <v>6943720</v>
+        <v>6943591</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15027,10 +15027,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121542288</v>
+        <v>121541348</v>
       </c>
       <c r="B128" t="n">
-        <v>56568</v>
+        <v>78609</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15039,43 +15039,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>491296</v>
+        <v>491203</v>
       </c>
       <c r="R128" t="n">
-        <v>6943697</v>
+        <v>6943563</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15107,7 +15102,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15117,7 +15112,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15144,10 +15139,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121541348</v>
+        <v>121542288</v>
       </c>
       <c r="B129" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15156,38 +15151,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>491203</v>
+        <v>491296</v>
       </c>
       <c r="R129" t="n">
-        <v>6943563</v>
+        <v>6943697</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15592,10 +15592,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121543021</v>
+        <v>121540656</v>
       </c>
       <c r="B133" t="n">
-        <v>78346</v>
+        <v>79690</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15608,34 +15608,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>490921</v>
+        <v>491058</v>
       </c>
       <c r="R133" t="n">
-        <v>6943724</v>
+        <v>6943647</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15816,10 +15816,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121540656</v>
+        <v>121543021</v>
       </c>
       <c r="B135" t="n">
-        <v>79690</v>
+        <v>78346</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15832,34 +15832,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491058</v>
+        <v>490921</v>
       </c>
       <c r="R135" t="n">
-        <v>6943647</v>
+        <v>6943724</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD135" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -13890,7 +13890,7 @@
         <v>121542668</v>
       </c>
       <c r="B118" t="n">
-        <v>56568</v>
+        <v>56569</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14014,10 +14014,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121542897</v>
+        <v>121543021</v>
       </c>
       <c r="B119" t="n">
-        <v>74707</v>
+        <v>78353</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14030,34 +14030,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>491325</v>
+        <v>490921</v>
       </c>
       <c r="R119" t="n">
-        <v>6943735</v>
+        <v>6943724</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14126,10 +14126,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121542839</v>
+        <v>121541303</v>
       </c>
       <c r="B120" t="n">
-        <v>78609</v>
+        <v>78353</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14142,21 +14142,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14166,10 +14166,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>491388</v>
+        <v>491256</v>
       </c>
       <c r="R120" t="n">
-        <v>6943720</v>
+        <v>6943499</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14238,10 +14238,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121541432</v>
+        <v>121540656</v>
       </c>
       <c r="B121" t="n">
-        <v>79691</v>
+        <v>79697</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14254,21 +14254,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>491187</v>
+        <v>491058</v>
       </c>
       <c r="R121" t="n">
-        <v>6943591</v>
+        <v>6943647</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14350,10 +14350,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121541418</v>
+        <v>121542288</v>
       </c>
       <c r="B122" t="n">
-        <v>82393</v>
+        <v>56569</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14362,38 +14362,43 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>491191</v>
+        <v>491296</v>
       </c>
       <c r="R122" t="n">
-        <v>6943589</v>
+        <v>6943697</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14425,7 +14430,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14435,7 +14440,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14462,10 +14467,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121541329</v>
+        <v>121540870</v>
       </c>
       <c r="B123" t="n">
-        <v>79198</v>
+        <v>79205</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14502,10 +14507,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>491215</v>
+        <v>491131</v>
       </c>
       <c r="R123" t="n">
-        <v>6943527</v>
+        <v>6943593</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14537,7 +14542,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14547,7 +14552,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14574,10 +14584,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121541195</v>
+        <v>121541432</v>
       </c>
       <c r="B124" t="n">
-        <v>78609</v>
+        <v>79698</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14590,34 +14600,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>491317</v>
+        <v>491187</v>
       </c>
       <c r="R124" t="n">
-        <v>6943408</v>
+        <v>6943591</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14649,7 +14659,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14659,7 +14669,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14686,10 +14696,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121540892</v>
+        <v>121541418</v>
       </c>
       <c r="B125" t="n">
-        <v>78609</v>
+        <v>82400</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14702,21 +14712,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14726,10 +14736,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>491148</v>
+        <v>491191</v>
       </c>
       <c r="R125" t="n">
-        <v>6943542</v>
+        <v>6943589</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14761,7 +14771,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14771,7 +14781,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14798,10 +14808,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121540870</v>
+        <v>121541348</v>
       </c>
       <c r="B126" t="n">
-        <v>79198</v>
+        <v>78616</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14814,21 +14824,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14838,10 +14848,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>491131</v>
+        <v>491203</v>
       </c>
       <c r="R126" t="n">
-        <v>6943593</v>
+        <v>6943563</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14873,7 +14883,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14883,12 +14893,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14915,10 +14920,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121541688</v>
+        <v>121540990</v>
       </c>
       <c r="B127" t="n">
-        <v>82393</v>
+        <v>78616</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14931,34 +14936,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>491221</v>
+        <v>491111</v>
       </c>
       <c r="R127" t="n">
-        <v>6943638</v>
+        <v>6943502</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14990,7 +14995,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15000,7 +15005,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15027,10 +15032,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121541348</v>
+        <v>121542897</v>
       </c>
       <c r="B128" t="n">
-        <v>78609</v>
+        <v>74714</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15043,34 +15048,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>491203</v>
+        <v>491325</v>
       </c>
       <c r="R128" t="n">
-        <v>6943563</v>
+        <v>6943735</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15102,7 +15107,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15112,7 +15117,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15139,10 +15144,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121542288</v>
+        <v>121540625</v>
       </c>
       <c r="B129" t="n">
-        <v>56568</v>
+        <v>79205</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15151,43 +15156,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>491296</v>
+        <v>491024</v>
       </c>
       <c r="R129" t="n">
-        <v>6943697</v>
+        <v>6943620</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15256,10 +15256,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121540990</v>
+        <v>121541493</v>
       </c>
       <c r="B130" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15272,21 +15272,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15296,10 +15296,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>491111</v>
+        <v>491173</v>
       </c>
       <c r="R130" t="n">
-        <v>6943502</v>
+        <v>6943600</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15368,10 +15368,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121540625</v>
+        <v>121541329</v>
       </c>
       <c r="B131" t="n">
-        <v>79198</v>
+        <v>79205</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>491024</v>
+        <v>491215</v>
       </c>
       <c r="R131" t="n">
-        <v>6943620</v>
+        <v>6943527</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15443,7 +15443,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15480,10 +15480,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121541303</v>
+        <v>121542839</v>
       </c>
       <c r="B132" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15496,21 +15496,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491256</v>
+        <v>491388</v>
       </c>
       <c r="R132" t="n">
-        <v>6943499</v>
+        <v>6943720</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15592,10 +15592,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121540656</v>
+        <v>121541599</v>
       </c>
       <c r="B133" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15608,34 +15608,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491058</v>
+        <v>491226</v>
       </c>
       <c r="R133" t="n">
-        <v>6943647</v>
+        <v>6943609</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15704,10 +15704,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121541599</v>
+        <v>121542322</v>
       </c>
       <c r="B134" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15744,10 +15744,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>491226</v>
+        <v>491303</v>
       </c>
       <c r="R134" t="n">
-        <v>6943609</v>
+        <v>6943695</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15789,7 +15789,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15816,10 +15816,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121543021</v>
+        <v>121541195</v>
       </c>
       <c r="B135" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15832,34 +15832,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>490921</v>
+        <v>491317</v>
       </c>
       <c r="R135" t="n">
-        <v>6943724</v>
+        <v>6943408</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15928,10 +15928,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121541493</v>
+        <v>121540892</v>
       </c>
       <c r="B136" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15944,21 +15944,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15968,10 +15968,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>491173</v>
+        <v>491148</v>
       </c>
       <c r="R136" t="n">
-        <v>6943600</v>
+        <v>6943542</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16040,10 +16040,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121542322</v>
+        <v>121541688</v>
       </c>
       <c r="B137" t="n">
-        <v>78609</v>
+        <v>82400</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16056,21 +16056,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16080,10 +16080,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>491303</v>
+        <v>491221</v>
       </c>
       <c r="R137" t="n">
-        <v>6943695</v>
+        <v>6943638</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16152,10 +16152,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121659358</v>
+        <v>121659363</v>
       </c>
       <c r="B138" t="n">
-        <v>55958</v>
+        <v>55959</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16193,14 +16193,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>491021</v>
+        <v>491314</v>
       </c>
       <c r="R138" t="n">
-        <v>6943660</v>
+        <v>6943736</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16259,10 +16259,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121659363</v>
+        <v>121659358</v>
       </c>
       <c r="B139" t="n">
-        <v>55958</v>
+        <v>55959</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16300,14 +16300,14 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>491314</v>
+        <v>491021</v>
       </c>
       <c r="R139" t="n">
-        <v>6943736</v>
+        <v>6943660</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY139"/>
+  <dimension ref="A1:AY141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15256,10 +15256,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121541493</v>
+        <v>121542839</v>
       </c>
       <c r="B130" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15272,34 +15272,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>491173</v>
+        <v>491388</v>
       </c>
       <c r="R130" t="n">
-        <v>6943600</v>
+        <v>6943720</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15368,10 +15368,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121541329</v>
+        <v>121541599</v>
       </c>
       <c r="B131" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15384,34 +15384,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>491215</v>
+        <v>491226</v>
       </c>
       <c r="R131" t="n">
-        <v>6943527</v>
+        <v>6943609</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15443,7 +15443,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15480,10 +15480,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121542839</v>
+        <v>121541493</v>
       </c>
       <c r="B132" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15496,34 +15496,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491388</v>
+        <v>491173</v>
       </c>
       <c r="R132" t="n">
-        <v>6943720</v>
+        <v>6943600</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15592,10 +15592,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121541599</v>
+        <v>121541329</v>
       </c>
       <c r="B133" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15608,34 +15608,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491226</v>
+        <v>491215</v>
       </c>
       <c r="R133" t="n">
-        <v>6943609</v>
+        <v>6943527</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16364,6 +16364,230 @@
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>121722526</v>
+      </c>
+      <c r="B140" t="n">
+        <v>79697</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>491203</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6943753</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2024-12-23</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2024-12-23</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>121722647</v>
+      </c>
+      <c r="B141" t="n">
+        <v>82400</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>491143</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6943750</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2024-12-23</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2024-12-23</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -13887,10 +13887,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121540656</v>
+        <v>121540990</v>
       </c>
       <c r="B118" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13903,21 +13903,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13927,10 +13927,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>491058</v>
+        <v>491111</v>
       </c>
       <c r="R118" t="n">
-        <v>6943647</v>
+        <v>6943502</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13999,10 +13999,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121540870</v>
+        <v>121542668</v>
       </c>
       <c r="B119" t="n">
-        <v>79205</v>
+        <v>56569</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14011,41 +14011,56 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>491131</v>
+        <v>491339</v>
       </c>
       <c r="R119" t="n">
-        <v>6943593</v>
+        <v>6943741</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14074,7 +14089,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14084,12 +14099,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14116,10 +14126,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121542322</v>
+        <v>121541432</v>
       </c>
       <c r="B120" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14132,34 +14142,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>491303</v>
+        <v>491187</v>
       </c>
       <c r="R120" t="n">
-        <v>6943695</v>
+        <v>6943591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14191,7 +14201,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14201,7 +14211,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14228,7 +14238,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121541329</v>
+        <v>121540625</v>
       </c>
       <c r="B121" t="n">
         <v>79205</v>
@@ -14268,10 +14278,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>491215</v>
+        <v>491024</v>
       </c>
       <c r="R121" t="n">
-        <v>6943527</v>
+        <v>6943620</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14303,7 +14313,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14313,7 +14323,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14340,10 +14350,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121540625</v>
+        <v>121541348</v>
       </c>
       <c r="B122" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14356,21 +14366,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14380,10 +14390,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>491024</v>
+        <v>491203</v>
       </c>
       <c r="R122" t="n">
-        <v>6943620</v>
+        <v>6943563</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14415,7 +14425,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14425,7 +14435,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14452,10 +14462,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121542288</v>
+        <v>121542839</v>
       </c>
       <c r="B123" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14464,43 +14474,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>491296</v>
+        <v>491388</v>
       </c>
       <c r="R123" t="n">
-        <v>6943697</v>
+        <v>6943720</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14532,7 +14537,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14542,7 +14547,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14569,7 +14574,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121541348</v>
+        <v>121541195</v>
       </c>
       <c r="B124" t="n">
         <v>78616</v>
@@ -14605,14 +14610,14 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>491203</v>
+        <v>491317</v>
       </c>
       <c r="R124" t="n">
-        <v>6943563</v>
+        <v>6943408</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14644,7 +14649,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14654,7 +14659,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14681,10 +14686,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121541688</v>
+        <v>121542322</v>
       </c>
       <c r="B125" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14697,21 +14702,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14721,10 +14726,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>491221</v>
+        <v>491303</v>
       </c>
       <c r="R125" t="n">
-        <v>6943638</v>
+        <v>6943695</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14756,7 +14761,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14766,7 +14771,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14793,10 +14798,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121542839</v>
+        <v>121541303</v>
       </c>
       <c r="B126" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14809,21 +14814,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14833,10 +14838,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>491388</v>
+        <v>491256</v>
       </c>
       <c r="R126" t="n">
-        <v>6943720</v>
+        <v>6943499</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14868,7 +14873,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14878,7 +14883,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14905,10 +14910,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121543021</v>
+        <v>121541599</v>
       </c>
       <c r="B127" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14921,34 +14926,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>490921</v>
+        <v>491226</v>
       </c>
       <c r="R127" t="n">
-        <v>6943724</v>
+        <v>6943609</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14980,7 +14985,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14990,7 +14995,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15017,10 +15022,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121541432</v>
+        <v>121543021</v>
       </c>
       <c r="B128" t="n">
-        <v>79698</v>
+        <v>78353</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15033,34 +15038,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>491187</v>
+        <v>490921</v>
       </c>
       <c r="R128" t="n">
-        <v>6943591</v>
+        <v>6943724</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15092,7 +15097,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15102,7 +15107,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15129,10 +15134,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121541599</v>
+        <v>121542288</v>
       </c>
       <c r="B129" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15141,38 +15146,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>491226</v>
+        <v>491296</v>
       </c>
       <c r="R129" t="n">
-        <v>6943609</v>
+        <v>6943697</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15204,7 +15214,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15214,7 +15224,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15241,10 +15251,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121541303</v>
+        <v>121541493</v>
       </c>
       <c r="B130" t="n">
-        <v>78353</v>
+        <v>79697</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15257,34 +15267,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>491256</v>
+        <v>491173</v>
       </c>
       <c r="R130" t="n">
-        <v>6943499</v>
+        <v>6943600</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15316,7 +15326,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15326,7 +15336,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15353,10 +15363,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121540892</v>
+        <v>121541418</v>
       </c>
       <c r="B131" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15369,21 +15379,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15393,10 +15403,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>491148</v>
+        <v>491191</v>
       </c>
       <c r="R131" t="n">
-        <v>6943542</v>
+        <v>6943589</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15428,7 +15438,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15438,7 +15448,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15465,10 +15475,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121542668</v>
+        <v>121541688</v>
       </c>
       <c r="B132" t="n">
-        <v>56569</v>
+        <v>82400</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15477,56 +15487,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491339</v>
+        <v>491221</v>
       </c>
       <c r="R132" t="n">
-        <v>6943741</v>
+        <v>6943638</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15555,7 +15550,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15565,7 +15560,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15592,10 +15587,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121541493</v>
+        <v>121540892</v>
       </c>
       <c r="B133" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15608,21 +15603,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15632,10 +15627,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491173</v>
+        <v>491148</v>
       </c>
       <c r="R133" t="n">
-        <v>6943600</v>
+        <v>6943542</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15667,7 +15662,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15677,7 +15672,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15704,10 +15699,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121541195</v>
+        <v>121540870</v>
       </c>
       <c r="B134" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15720,34 +15715,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>491317</v>
+        <v>491131</v>
       </c>
       <c r="R134" t="n">
-        <v>6943408</v>
+        <v>6943593</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15779,7 +15774,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15789,7 +15784,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15816,10 +15816,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121541418</v>
+        <v>121540656</v>
       </c>
       <c r="B135" t="n">
-        <v>82400</v>
+        <v>79697</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15832,21 +15832,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15856,10 +15856,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491191</v>
+        <v>491058</v>
       </c>
       <c r="R135" t="n">
-        <v>6943589</v>
+        <v>6943647</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15928,10 +15928,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121540990</v>
+        <v>121541329</v>
       </c>
       <c r="B136" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15944,21 +15944,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15968,10 +15968,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>491111</v>
+        <v>491215</v>
       </c>
       <c r="R136" t="n">
-        <v>6943502</v>
+        <v>6943527</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16152,7 +16152,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121659358</v>
+        <v>121659363</v>
       </c>
       <c r="B138" t="n">
         <v>55959</v>
@@ -16193,14 +16193,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>491021</v>
+        <v>491314</v>
       </c>
       <c r="R138" t="n">
-        <v>6943660</v>
+        <v>6943736</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16259,7 +16259,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121659363</v>
+        <v>121659358</v>
       </c>
       <c r="B139" t="n">
         <v>55959</v>
@@ -16300,14 +16300,14 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>491314</v>
+        <v>491021</v>
       </c>
       <c r="R139" t="n">
-        <v>6943736</v>
+        <v>6943660</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -14910,10 +14910,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121541599</v>
+        <v>121543021</v>
       </c>
       <c r="B127" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14926,34 +14926,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>491226</v>
+        <v>490921</v>
       </c>
       <c r="R127" t="n">
-        <v>6943609</v>
+        <v>6943724</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14985,7 +14985,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15022,10 +15022,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121543021</v>
+        <v>121541599</v>
       </c>
       <c r="B128" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15038,34 +15038,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>490921</v>
+        <v>491226</v>
       </c>
       <c r="R128" t="n">
-        <v>6943724</v>
+        <v>6943609</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15107,7 +15107,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD128" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -13887,10 +13887,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121540990</v>
+        <v>121541329</v>
       </c>
       <c r="B118" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13903,21 +13903,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13927,10 +13927,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>491111</v>
+        <v>491215</v>
       </c>
       <c r="R118" t="n">
-        <v>6943502</v>
+        <v>6943527</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13999,10 +13999,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121542668</v>
+        <v>121541303</v>
       </c>
       <c r="B119" t="n">
-        <v>56569</v>
+        <v>78353</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14011,56 +14011,41 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>491339</v>
+        <v>491256</v>
       </c>
       <c r="R119" t="n">
-        <v>6943741</v>
+        <v>6943499</v>
       </c>
       <c r="S119" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14089,7 +14074,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14099,7 +14084,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14126,10 +14111,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121541432</v>
+        <v>121540656</v>
       </c>
       <c r="B120" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14142,21 +14127,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14166,10 +14151,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>491187</v>
+        <v>491058</v>
       </c>
       <c r="R120" t="n">
-        <v>6943591</v>
+        <v>6943647</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14201,7 +14186,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14211,7 +14196,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14238,10 +14223,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121540625</v>
+        <v>121541688</v>
       </c>
       <c r="B121" t="n">
-        <v>79205</v>
+        <v>82400</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14254,34 +14239,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>491024</v>
+        <v>491221</v>
       </c>
       <c r="R121" t="n">
-        <v>6943620</v>
+        <v>6943638</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14313,7 +14298,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14323,7 +14308,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14350,7 +14335,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121541348</v>
+        <v>121541195</v>
       </c>
       <c r="B122" t="n">
         <v>78616</v>
@@ -14386,14 +14371,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>491203</v>
+        <v>491317</v>
       </c>
       <c r="R122" t="n">
-        <v>6943563</v>
+        <v>6943408</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14425,7 +14410,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14435,7 +14420,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14462,10 +14447,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121542839</v>
+        <v>121540870</v>
       </c>
       <c r="B123" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14478,34 +14463,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>491388</v>
+        <v>491131</v>
       </c>
       <c r="R123" t="n">
-        <v>6943720</v>
+        <v>6943593</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14537,7 +14522,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14547,7 +14532,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14574,7 +14564,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121541195</v>
+        <v>121542322</v>
       </c>
       <c r="B124" t="n">
         <v>78616</v>
@@ -14614,10 +14604,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>491317</v>
+        <v>491303</v>
       </c>
       <c r="R124" t="n">
-        <v>6943408</v>
+        <v>6943695</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14649,7 +14639,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14659,7 +14649,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14686,10 +14676,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121542322</v>
+        <v>121542897</v>
       </c>
       <c r="B125" t="n">
-        <v>78616</v>
+        <v>74714</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14702,21 +14692,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14726,10 +14716,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>491303</v>
+        <v>491325</v>
       </c>
       <c r="R125" t="n">
-        <v>6943695</v>
+        <v>6943735</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14761,7 +14751,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14771,7 +14761,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14798,10 +14788,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121541303</v>
+        <v>121541348</v>
       </c>
       <c r="B126" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14814,34 +14804,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>491256</v>
+        <v>491203</v>
       </c>
       <c r="R126" t="n">
-        <v>6943499</v>
+        <v>6943563</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14873,7 +14863,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14883,7 +14873,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14910,10 +14900,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121543021</v>
+        <v>121542839</v>
       </c>
       <c r="B127" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14926,34 +14916,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>490921</v>
+        <v>491388</v>
       </c>
       <c r="R127" t="n">
-        <v>6943724</v>
+        <v>6943720</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14985,7 +14975,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14995,7 +14985,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15022,10 +15012,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121541599</v>
+        <v>121541418</v>
       </c>
       <c r="B128" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15038,34 +15028,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>491226</v>
+        <v>491191</v>
       </c>
       <c r="R128" t="n">
-        <v>6943609</v>
+        <v>6943589</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15097,7 +15087,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15107,7 +15097,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15134,10 +15124,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121542288</v>
+        <v>121541493</v>
       </c>
       <c r="B129" t="n">
-        <v>56569</v>
+        <v>79697</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15146,43 +15136,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>491296</v>
+        <v>491173</v>
       </c>
       <c r="R129" t="n">
-        <v>6943697</v>
+        <v>6943600</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15214,7 +15199,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15224,7 +15209,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15251,10 +15236,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121541493</v>
+        <v>121542288</v>
       </c>
       <c r="B130" t="n">
-        <v>79697</v>
+        <v>56569</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15263,38 +15248,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>491173</v>
+        <v>491296</v>
       </c>
       <c r="R130" t="n">
-        <v>6943600</v>
+        <v>6943697</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15326,7 +15316,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15336,7 +15326,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15363,10 +15353,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121541418</v>
+        <v>121540892</v>
       </c>
       <c r="B131" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15379,21 +15369,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15403,10 +15393,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>491191</v>
+        <v>491148</v>
       </c>
       <c r="R131" t="n">
-        <v>6943589</v>
+        <v>6943542</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15438,7 +15428,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15448,7 +15438,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15475,10 +15465,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121541688</v>
+        <v>121541432</v>
       </c>
       <c r="B132" t="n">
-        <v>82400</v>
+        <v>79698</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15491,34 +15481,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491221</v>
+        <v>491187</v>
       </c>
       <c r="R132" t="n">
-        <v>6943638</v>
+        <v>6943591</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15550,7 +15540,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15560,7 +15550,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15587,7 +15577,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121540892</v>
+        <v>121540990</v>
       </c>
       <c r="B133" t="n">
         <v>78616</v>
@@ -15627,10 +15617,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491148</v>
+        <v>491111</v>
       </c>
       <c r="R133" t="n">
-        <v>6943542</v>
+        <v>6943502</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15662,7 +15652,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15672,7 +15662,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15699,10 +15689,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121540870</v>
+        <v>121542668</v>
       </c>
       <c r="B134" t="n">
-        <v>79205</v>
+        <v>56569</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15711,41 +15701,56 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>491131</v>
+        <v>491339</v>
       </c>
       <c r="R134" t="n">
-        <v>6943593</v>
+        <v>6943741</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15774,7 +15779,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15784,12 +15789,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Gammal hällmarksskog med senvuxen tall och en hel del solbelyst död ved.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15816,10 +15816,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121540656</v>
+        <v>121543021</v>
       </c>
       <c r="B135" t="n">
-        <v>79697</v>
+        <v>78353</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15832,34 +15832,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491058</v>
+        <v>490921</v>
       </c>
       <c r="R135" t="n">
-        <v>6943647</v>
+        <v>6943724</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15928,10 +15928,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121541329</v>
+        <v>121541599</v>
       </c>
       <c r="B136" t="n">
-        <v>79205</v>
+        <v>78616</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15944,34 +15944,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>491215</v>
+        <v>491226</v>
       </c>
       <c r="R136" t="n">
-        <v>6943527</v>
+        <v>6943609</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16040,10 +16040,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121542897</v>
+        <v>121540625</v>
       </c>
       <c r="B137" t="n">
-        <v>74714</v>
+        <v>79205</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16056,34 +16056,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>308</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>491325</v>
+        <v>491024</v>
       </c>
       <c r="R137" t="n">
-        <v>6943735</v>
+        <v>6943620</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16152,7 +16152,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121659363</v>
+        <v>121659358</v>
       </c>
       <c r="B138" t="n">
         <v>55959</v>
@@ -16193,14 +16193,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>491314</v>
+        <v>491021</v>
       </c>
       <c r="R138" t="n">
-        <v>6943736</v>
+        <v>6943660</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16259,7 +16259,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121659358</v>
+        <v>121659363</v>
       </c>
       <c r="B139" t="n">
         <v>55959</v>
@@ -16300,14 +16300,14 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Salomsmyren, Lill-Salomsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>491021</v>
+        <v>491314</v>
       </c>
       <c r="R139" t="n">
-        <v>6943660</v>
+        <v>6943736</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -16914,7 +16914,7 @@
         <v>125747725</v>
       </c>
       <c r="B145" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125747107</v>
+        <v>125748931</v>
       </c>
       <c r="B148" t="n">
-        <v>80071</v>
+        <v>78634</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17243,21 +17243,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17267,10 +17267,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491155</v>
+        <v>491231</v>
       </c>
       <c r="R148" t="n">
-        <v>6943388</v>
+        <v>6943501</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17339,10 +17339,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125748931</v>
+        <v>125747107</v>
       </c>
       <c r="B149" t="n">
-        <v>78634</v>
+        <v>80071</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17350,21 +17350,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17374,10 +17374,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491231</v>
+        <v>491155</v>
       </c>
       <c r="R149" t="n">
-        <v>6943501</v>
+        <v>6943388</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17446,32 +17446,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125748742</v>
+        <v>125748199</v>
       </c>
       <c r="B150" t="n">
-        <v>77916</v>
+        <v>98331</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17481,10 +17481,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>491226</v>
+        <v>491217</v>
       </c>
       <c r="R150" t="n">
-        <v>6943499</v>
+        <v>6943452</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17553,32 +17553,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125748199</v>
+        <v>125748742</v>
       </c>
       <c r="B151" t="n">
-        <v>98324</v>
+        <v>77916</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17588,10 +17588,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>491217</v>
+        <v>491226</v>
       </c>
       <c r="R151" t="n">
-        <v>6943452</v>
+        <v>6943499</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18080,7 +18080,7 @@
         <v>125771024</v>
       </c>
       <c r="B156" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>125771144</v>
       </c>
       <c r="B157" t="n">
-        <v>91478</v>
+        <v>91485</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>125807676</v>
       </c>
       <c r="B160" t="n">
-        <v>88626</v>
+        <v>88633</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>125807674</v>
       </c>
       <c r="B165" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19047,35 +19047,40 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125807672</v>
+        <v>125807671</v>
       </c>
       <c r="B166" t="n">
-        <v>91240</v>
+        <v>56843</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19085,7 +19090,7 @@
         <v>491200</v>
       </c>
       <c r="R166" t="n">
-        <v>6943480</v>
+        <v>6943467</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -19144,40 +19149,35 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125807671</v>
+        <v>125807672</v>
       </c>
       <c r="B167" t="n">
-        <v>56843</v>
+        <v>91247</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19187,7 +19187,7 @@
         <v>491200</v>
       </c>
       <c r="R167" t="n">
-        <v>6943467</v>
+        <v>6943480</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -18274,7 +18274,7 @@
         <v>125807675</v>
       </c>
       <c r="B158" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>125807677</v>
       </c>
       <c r="B159" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>125807676</v>
       </c>
       <c r="B160" t="n">
-        <v>88633</v>
+        <v>88637</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>125807673</v>
       </c>
       <c r="B161" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>125807678</v>
       </c>
       <c r="B162" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>125807669</v>
       </c>
       <c r="B163" t="n">
-        <v>78991</v>
+        <v>78992</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>125807670</v>
       </c>
       <c r="B164" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>125807674</v>
       </c>
       <c r="B165" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>125807672</v>
       </c>
       <c r="B167" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>125770743</v>
       </c>
       <c r="B168" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -16593,7 +16593,7 @@
         <v>125749113</v>
       </c>
       <c r="B142" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>125747830</v>
       </c>
       <c r="B143" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>125748749</v>
       </c>
       <c r="B144" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>125747725</v>
       </c>
       <c r="B145" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>125747114</v>
       </c>
       <c r="B146" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17125,32 +17125,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125747204</v>
+        <v>125748931</v>
       </c>
       <c r="B147" t="n">
-        <v>80098</v>
+        <v>78635</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491191</v>
+        <v>491231</v>
       </c>
       <c r="R147" t="n">
-        <v>6943346</v>
+        <v>6943501</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17232,10 +17232,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125748931</v>
+        <v>125747107</v>
       </c>
       <c r="B148" t="n">
-        <v>78634</v>
+        <v>80072</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17243,21 +17243,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17267,10 +17267,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491231</v>
+        <v>491155</v>
       </c>
       <c r="R148" t="n">
-        <v>6943501</v>
+        <v>6943388</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17339,32 +17339,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125747107</v>
+        <v>125747204</v>
       </c>
       <c r="B149" t="n">
-        <v>80071</v>
+        <v>80099</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17374,10 +17374,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491155</v>
+        <v>491191</v>
       </c>
       <c r="R149" t="n">
-        <v>6943388</v>
+        <v>6943346</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17449,7 +17449,7 @@
         <v>125748199</v>
       </c>
       <c r="B150" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>125748742</v>
       </c>
       <c r="B151" t="n">
-        <v>77916</v>
+        <v>77917</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>125753755</v>
       </c>
       <c r="B152" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>125748705</v>
       </c>
       <c r="B153" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>125770538</v>
       </c>
       <c r="B154" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>125769296</v>
       </c>
       <c r="B155" t="n">
-        <v>79053</v>
+        <v>79054</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>125771024</v>
       </c>
       <c r="B156" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>125771144</v>
       </c>
       <c r="B157" t="n">
-        <v>91485</v>
+        <v>91489</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19047,40 +19047,35 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125807671</v>
+        <v>125807672</v>
       </c>
       <c r="B166" t="n">
-        <v>56843</v>
+        <v>91248</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19090,7 +19085,7 @@
         <v>491200</v>
       </c>
       <c r="R166" t="n">
-        <v>6943467</v>
+        <v>6943480</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -19149,35 +19144,40 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125807672</v>
+        <v>125807671</v>
       </c>
       <c r="B167" t="n">
-        <v>91248</v>
+        <v>56843</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19187,7 +19187,7 @@
         <v>491200</v>
       </c>
       <c r="R167" t="n">
-        <v>6943480</v>
+        <v>6943467</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -16593,7 +16593,7 @@
         <v>125749113</v>
       </c>
       <c r="B142" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>125747830</v>
       </c>
       <c r="B143" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>125748749</v>
       </c>
       <c r="B144" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>125747725</v>
       </c>
       <c r="B145" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>125747114</v>
       </c>
       <c r="B146" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>125748931</v>
       </c>
       <c r="B147" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17232,32 +17232,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125747107</v>
+        <v>125747204</v>
       </c>
       <c r="B148" t="n">
-        <v>80072</v>
+        <v>80103</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17267,10 +17267,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491155</v>
+        <v>491191</v>
       </c>
       <c r="R148" t="n">
-        <v>6943388</v>
+        <v>6943346</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17339,32 +17339,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125747204</v>
+        <v>125747107</v>
       </c>
       <c r="B149" t="n">
-        <v>80099</v>
+        <v>80076</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17374,10 +17374,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491191</v>
+        <v>491155</v>
       </c>
       <c r="R149" t="n">
-        <v>6943346</v>
+        <v>6943388</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17446,32 +17446,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125748199</v>
+        <v>125748742</v>
       </c>
       <c r="B150" t="n">
-        <v>98334</v>
+        <v>77921</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17481,10 +17481,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>491217</v>
+        <v>491226</v>
       </c>
       <c r="R150" t="n">
-        <v>6943452</v>
+        <v>6943499</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17553,32 +17553,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125748742</v>
+        <v>125748199</v>
       </c>
       <c r="B151" t="n">
-        <v>77917</v>
+        <v>98338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17588,10 +17588,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>491226</v>
+        <v>491217</v>
       </c>
       <c r="R151" t="n">
-        <v>6943499</v>
+        <v>6943452</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17663,7 +17663,7 @@
         <v>125753755</v>
       </c>
       <c r="B152" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>125748705</v>
       </c>
       <c r="B153" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>125770538</v>
       </c>
       <c r="B154" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>125769296</v>
       </c>
       <c r="B155" t="n">
-        <v>79054</v>
+        <v>79058</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>125771024</v>
       </c>
       <c r="B156" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>125771144</v>
       </c>
       <c r="B157" t="n">
-        <v>91489</v>
+        <v>91493</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>125807675</v>
       </c>
       <c r="B158" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>125807677</v>
       </c>
       <c r="B159" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>125807676</v>
       </c>
       <c r="B160" t="n">
-        <v>88637</v>
+        <v>88641</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>125807673</v>
       </c>
       <c r="B161" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>125807678</v>
       </c>
       <c r="B162" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>125807669</v>
       </c>
       <c r="B163" t="n">
-        <v>78992</v>
+        <v>78996</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>125807670</v>
       </c>
       <c r="B164" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>125807674</v>
       </c>
       <c r="B165" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>125807672</v>
       </c>
       <c r="B166" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>125770743</v>
       </c>
       <c r="B168" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -17125,32 +17125,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125748931</v>
+        <v>125747204</v>
       </c>
       <c r="B147" t="n">
-        <v>78639</v>
+        <v>80103</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491231</v>
+        <v>491191</v>
       </c>
       <c r="R147" t="n">
-        <v>6943501</v>
+        <v>6943346</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17232,32 +17232,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125747204</v>
+        <v>125748931</v>
       </c>
       <c r="B148" t="n">
-        <v>80103</v>
+        <v>78639</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17267,10 +17267,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491191</v>
+        <v>491231</v>
       </c>
       <c r="R148" t="n">
-        <v>6943346</v>
+        <v>6943501</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17446,32 +17446,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125748742</v>
+        <v>125748199</v>
       </c>
       <c r="B150" t="n">
-        <v>77921</v>
+        <v>98339</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17481,10 +17481,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>491226</v>
+        <v>491217</v>
       </c>
       <c r="R150" t="n">
-        <v>6943499</v>
+        <v>6943452</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17553,32 +17553,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125748199</v>
+        <v>125748742</v>
       </c>
       <c r="B151" t="n">
-        <v>98338</v>
+        <v>77921</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17588,10 +17588,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>491217</v>
+        <v>491226</v>
       </c>
       <c r="R151" t="n">
-        <v>6943452</v>
+        <v>6943499</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -17125,32 +17125,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125747204</v>
+        <v>125748931</v>
       </c>
       <c r="B147" t="n">
-        <v>80103</v>
+        <v>78639</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491191</v>
+        <v>491231</v>
       </c>
       <c r="R147" t="n">
-        <v>6943346</v>
+        <v>6943501</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17232,32 +17232,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125748931</v>
+        <v>125747204</v>
       </c>
       <c r="B148" t="n">
-        <v>78639</v>
+        <v>80103</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17267,10 +17267,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491231</v>
+        <v>491191</v>
       </c>
       <c r="R148" t="n">
-        <v>6943501</v>
+        <v>6943346</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD148" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -17125,32 +17125,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125748931</v>
+        <v>125747204</v>
       </c>
       <c r="B147" t="n">
-        <v>78639</v>
+        <v>80103</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491231</v>
+        <v>491191</v>
       </c>
       <c r="R147" t="n">
-        <v>6943501</v>
+        <v>6943346</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17232,32 +17232,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125747204</v>
+        <v>125748931</v>
       </c>
       <c r="B148" t="n">
-        <v>80103</v>
+        <v>78639</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17267,10 +17267,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491191</v>
+        <v>491231</v>
       </c>
       <c r="R148" t="n">
-        <v>6943346</v>
+        <v>6943501</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD148" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -16593,7 +16593,7 @@
         <v>125749113</v>
       </c>
       <c r="B142" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>125747830</v>
       </c>
       <c r="B143" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>125748749</v>
       </c>
       <c r="B144" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>125747725</v>
       </c>
       <c r="B145" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>125747114</v>
       </c>
       <c r="B146" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17125,32 +17125,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125747204</v>
+        <v>125748931</v>
       </c>
       <c r="B147" t="n">
-        <v>80103</v>
+        <v>78640</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491191</v>
+        <v>491231</v>
       </c>
       <c r="R147" t="n">
-        <v>6943346</v>
+        <v>6943501</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17232,32 +17232,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125748931</v>
+        <v>125747204</v>
       </c>
       <c r="B148" t="n">
-        <v>78639</v>
+        <v>80104</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17267,10 +17267,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491231</v>
+        <v>491191</v>
       </c>
       <c r="R148" t="n">
-        <v>6943501</v>
+        <v>6943346</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17342,7 +17342,7 @@
         <v>125747107</v>
       </c>
       <c r="B149" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>125748199</v>
       </c>
       <c r="B150" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>125748742</v>
       </c>
       <c r="B151" t="n">
-        <v>77921</v>
+        <v>77922</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>125753755</v>
       </c>
       <c r="B152" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>125748705</v>
       </c>
       <c r="B153" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>125770538</v>
       </c>
       <c r="B154" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>125769296</v>
       </c>
       <c r="B155" t="n">
-        <v>79058</v>
+        <v>79059</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>125771024</v>
       </c>
       <c r="B156" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>125771144</v>
       </c>
       <c r="B157" t="n">
-        <v>91493</v>
+        <v>91495</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>125807675</v>
       </c>
       <c r="B158" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>125807677</v>
       </c>
       <c r="B159" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>125807676</v>
       </c>
       <c r="B160" t="n">
-        <v>88641</v>
+        <v>88643</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>125807673</v>
       </c>
       <c r="B161" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>125807678</v>
       </c>
       <c r="B162" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>125807669</v>
       </c>
       <c r="B163" t="n">
-        <v>78996</v>
+        <v>78997</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>125807670</v>
       </c>
       <c r="B164" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>125807674</v>
       </c>
       <c r="B165" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19047,35 +19047,40 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125807672</v>
+        <v>125807671</v>
       </c>
       <c r="B166" t="n">
-        <v>91252</v>
+        <v>56844</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19085,7 +19090,7 @@
         <v>491200</v>
       </c>
       <c r="R166" t="n">
-        <v>6943480</v>
+        <v>6943467</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -19144,40 +19149,35 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125807671</v>
+        <v>125807672</v>
       </c>
       <c r="B167" t="n">
-        <v>56843</v>
+        <v>91254</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19187,7 +19187,7 @@
         <v>491200</v>
       </c>
       <c r="R167" t="n">
-        <v>6943467</v>
+        <v>6943480</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -19249,7 +19249,7 @@
         <v>125770743</v>
       </c>
       <c r="B168" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -17125,10 +17125,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125748931</v>
+        <v>125747107</v>
       </c>
       <c r="B147" t="n">
-        <v>78640</v>
+        <v>80077</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17136,21 +17136,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491231</v>
+        <v>491155</v>
       </c>
       <c r="R147" t="n">
-        <v>6943501</v>
+        <v>6943388</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17232,32 +17232,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125747204</v>
+        <v>125748931</v>
       </c>
       <c r="B148" t="n">
-        <v>80104</v>
+        <v>78640</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17267,10 +17267,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491191</v>
+        <v>491231</v>
       </c>
       <c r="R148" t="n">
-        <v>6943346</v>
+        <v>6943501</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17339,32 +17339,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125747107</v>
+        <v>125747204</v>
       </c>
       <c r="B149" t="n">
-        <v>80077</v>
+        <v>80104</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17374,10 +17374,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491155</v>
+        <v>491191</v>
       </c>
       <c r="R149" t="n">
-        <v>6943388</v>
+        <v>6943346</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17446,32 +17446,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125748199</v>
+        <v>125748742</v>
       </c>
       <c r="B150" t="n">
-        <v>98341</v>
+        <v>77922</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17481,10 +17481,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>491217</v>
+        <v>491226</v>
       </c>
       <c r="R150" t="n">
-        <v>6943452</v>
+        <v>6943499</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17553,32 +17553,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125748742</v>
+        <v>125748199</v>
       </c>
       <c r="B151" t="n">
-        <v>77922</v>
+        <v>98341</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17588,10 +17588,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>491226</v>
+        <v>491217</v>
       </c>
       <c r="R151" t="n">
-        <v>6943499</v>
+        <v>6943452</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -16914,7 +16914,7 @@
         <v>125747725</v>
       </c>
       <c r="B145" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17232,32 +17232,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125748931</v>
+        <v>125747204</v>
       </c>
       <c r="B148" t="n">
-        <v>78640</v>
+        <v>80104</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17267,10 +17267,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491231</v>
+        <v>491191</v>
       </c>
       <c r="R148" t="n">
-        <v>6943501</v>
+        <v>6943346</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17339,32 +17339,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125747204</v>
+        <v>125748931</v>
       </c>
       <c r="B149" t="n">
-        <v>80104</v>
+        <v>78640</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17374,10 +17374,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491191</v>
+        <v>491231</v>
       </c>
       <c r="R149" t="n">
-        <v>6943346</v>
+        <v>6943501</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17556,7 +17556,7 @@
         <v>125748199</v>
       </c>
       <c r="B151" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>125771024</v>
       </c>
       <c r="B156" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>125771144</v>
       </c>
       <c r="B157" t="n">
-        <v>91495</v>
+        <v>91497</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>125807676</v>
       </c>
       <c r="B160" t="n">
-        <v>88643</v>
+        <v>88645</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>125807674</v>
       </c>
       <c r="B165" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19047,40 +19047,35 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125807671</v>
+        <v>125807672</v>
       </c>
       <c r="B166" t="n">
-        <v>56844</v>
+        <v>91256</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19090,7 +19085,7 @@
         <v>491200</v>
       </c>
       <c r="R166" t="n">
-        <v>6943467</v>
+        <v>6943480</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -19149,35 +19144,40 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125807672</v>
+        <v>125807671</v>
       </c>
       <c r="B167" t="n">
-        <v>91254</v>
+        <v>56844</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19187,7 +19187,7 @@
         <v>491200</v>
       </c>
       <c r="R167" t="n">
-        <v>6943480</v>
+        <v>6943467</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -17125,32 +17125,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125747107</v>
+        <v>125747204</v>
       </c>
       <c r="B147" t="n">
-        <v>80077</v>
+        <v>80104</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491155</v>
+        <v>491191</v>
       </c>
       <c r="R147" t="n">
-        <v>6943388</v>
+        <v>6943346</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17232,32 +17232,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125747204</v>
+        <v>125747107</v>
       </c>
       <c r="B148" t="n">
-        <v>80104</v>
+        <v>80077</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17267,10 +17267,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491191</v>
+        <v>491155</v>
       </c>
       <c r="R148" t="n">
-        <v>6943346</v>
+        <v>6943388</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD148" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -16914,7 +16914,7 @@
         <v>125747725</v>
       </c>
       <c r="B145" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17125,32 +17125,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125747204</v>
+        <v>125748931</v>
       </c>
       <c r="B147" t="n">
-        <v>80104</v>
+        <v>78640</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491191</v>
+        <v>491231</v>
       </c>
       <c r="R147" t="n">
-        <v>6943346</v>
+        <v>6943501</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17339,32 +17339,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125748931</v>
+        <v>125747204</v>
       </c>
       <c r="B149" t="n">
-        <v>78640</v>
+        <v>80104</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17374,10 +17374,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491231</v>
+        <v>491191</v>
       </c>
       <c r="R149" t="n">
-        <v>6943501</v>
+        <v>6943346</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17556,7 +17556,7 @@
         <v>125748199</v>
       </c>
       <c r="B151" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>125771024</v>
       </c>
       <c r="B156" t="n">
-        <v>92718</v>
+        <v>92720</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>125771144</v>
       </c>
       <c r="B157" t="n">
-        <v>91497</v>
+        <v>91499</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>125807676</v>
       </c>
       <c r="B160" t="n">
-        <v>88645</v>
+        <v>88647</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>125807674</v>
       </c>
       <c r="B165" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19047,35 +19047,40 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125807672</v>
+        <v>125807671</v>
       </c>
       <c r="B166" t="n">
-        <v>91256</v>
+        <v>56844</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19085,7 +19090,7 @@
         <v>491200</v>
       </c>
       <c r="R166" t="n">
-        <v>6943480</v>
+        <v>6943467</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -19144,40 +19149,35 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125807671</v>
+        <v>125807672</v>
       </c>
       <c r="B167" t="n">
-        <v>56844</v>
+        <v>91258</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19187,7 +19187,7 @@
         <v>491200</v>
       </c>
       <c r="R167" t="n">
-        <v>6943467</v>
+        <v>6943480</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -16593,7 +16593,7 @@
         <v>125749113</v>
       </c>
       <c r="B142" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>125747830</v>
       </c>
       <c r="B143" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>125748749</v>
       </c>
       <c r="B144" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>125747725</v>
       </c>
       <c r="B145" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>125747114</v>
       </c>
       <c r="B146" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>125748931</v>
       </c>
       <c r="B147" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>125747107</v>
       </c>
       <c r="B148" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>125747204</v>
       </c>
       <c r="B149" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17446,32 +17446,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125748742</v>
+        <v>125748199</v>
       </c>
       <c r="B150" t="n">
-        <v>77922</v>
+        <v>98349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17481,10 +17481,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>491226</v>
+        <v>491217</v>
       </c>
       <c r="R150" t="n">
-        <v>6943499</v>
+        <v>6943452</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17553,32 +17553,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125748199</v>
+        <v>125748742</v>
       </c>
       <c r="B151" t="n">
-        <v>98345</v>
+        <v>77926</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17588,10 +17588,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>491217</v>
+        <v>491226</v>
       </c>
       <c r="R151" t="n">
-        <v>6943452</v>
+        <v>6943499</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17663,7 +17663,7 @@
         <v>125753755</v>
       </c>
       <c r="B152" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>125748705</v>
       </c>
       <c r="B153" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>125770538</v>
       </c>
       <c r="B154" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>125769296</v>
       </c>
       <c r="B155" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>125771024</v>
       </c>
       <c r="B156" t="n">
-        <v>92720</v>
+        <v>92724</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>125771144</v>
       </c>
       <c r="B157" t="n">
-        <v>91499</v>
+        <v>91503</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>125807675</v>
       </c>
       <c r="B158" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>125807677</v>
       </c>
       <c r="B159" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>125807676</v>
       </c>
       <c r="B160" t="n">
-        <v>88647</v>
+        <v>88651</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>125807673</v>
       </c>
       <c r="B161" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>125807678</v>
       </c>
       <c r="B162" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>125807669</v>
       </c>
       <c r="B163" t="n">
-        <v>78997</v>
+        <v>79001</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>125807670</v>
       </c>
       <c r="B164" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>125807674</v>
       </c>
       <c r="B165" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19047,40 +19047,35 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125807671</v>
+        <v>125807672</v>
       </c>
       <c r="B166" t="n">
-        <v>56844</v>
+        <v>91262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19090,7 +19085,7 @@
         <v>491200</v>
       </c>
       <c r="R166" t="n">
-        <v>6943467</v>
+        <v>6943480</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -19149,35 +19144,40 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125807672</v>
+        <v>125807671</v>
       </c>
       <c r="B167" t="n">
-        <v>91258</v>
+        <v>56848</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Storörevattnet, Jmt</t>
@@ -19187,7 +19187,7 @@
         <v>491200</v>
       </c>
       <c r="R167" t="n">
-        <v>6943480</v>
+        <v>6943467</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -19249,7 +19249,7 @@
         <v>125770743</v>
       </c>
       <c r="B168" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -17446,32 +17446,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125748199</v>
+        <v>125748742</v>
       </c>
       <c r="B150" t="n">
-        <v>98349</v>
+        <v>77926</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17481,10 +17481,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>491217</v>
+        <v>491226</v>
       </c>
       <c r="R150" t="n">
-        <v>6943452</v>
+        <v>6943499</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17553,32 +17553,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125748742</v>
+        <v>125748199</v>
       </c>
       <c r="B151" t="n">
-        <v>77926</v>
+        <v>98349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17588,10 +17588,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>491226</v>
+        <v>491217</v>
       </c>
       <c r="R151" t="n">
-        <v>6943499</v>
+        <v>6943452</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -17556,7 +17556,7 @@
         <v>125748199</v>
       </c>
       <c r="B151" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -17125,32 +17125,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125748931</v>
+        <v>125747204</v>
       </c>
       <c r="B147" t="n">
-        <v>78644</v>
+        <v>80108</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491231</v>
+        <v>491191</v>
       </c>
       <c r="R147" t="n">
-        <v>6943501</v>
+        <v>6943346</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17339,32 +17339,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125747204</v>
+        <v>125748931</v>
       </c>
       <c r="B149" t="n">
-        <v>80108</v>
+        <v>78644</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17374,10 +17374,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491191</v>
+        <v>491231</v>
       </c>
       <c r="R149" t="n">
-        <v>6943346</v>
+        <v>6943501</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17446,32 +17446,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125748742</v>
+        <v>125748199</v>
       </c>
       <c r="B150" t="n">
-        <v>77926</v>
+        <v>98352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17481,10 +17481,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>491226</v>
+        <v>491217</v>
       </c>
       <c r="R150" t="n">
-        <v>6943499</v>
+        <v>6943452</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17553,32 +17553,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125748199</v>
+        <v>125748742</v>
       </c>
       <c r="B151" t="n">
-        <v>98352</v>
+        <v>77926</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17588,10 +17588,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>491217</v>
+        <v>491226</v>
       </c>
       <c r="R151" t="n">
-        <v>6943452</v>
+        <v>6943499</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -18274,7 +18274,7 @@
         <v>125807675</v>
       </c>
       <c r="B158" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>125807677</v>
       </c>
       <c r="B159" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>125807676</v>
       </c>
       <c r="B160" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>125807673</v>
       </c>
       <c r="B161" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>125807678</v>
       </c>
       <c r="B162" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>125807669</v>
       </c>
       <c r="B163" t="n">
-        <v>79001</v>
+        <v>79004</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>125807670</v>
       </c>
       <c r="B164" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>125807674</v>
       </c>
       <c r="B165" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>125807672</v>
       </c>
       <c r="B166" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>125807671</v>
       </c>
       <c r="B167" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>125770743</v>
       </c>
       <c r="B168" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY168"/>
+  <dimension ref="A1:AY191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19355,6 +19355,2364 @@
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>126521894</v>
+      </c>
+      <c r="B169" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Stor -Öravattnet, Stor -Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>491248</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6943265</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>126523129</v>
+      </c>
+      <c r="B170" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>491352</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6943338</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>126528439</v>
+      </c>
+      <c r="B171" t="n">
+        <v>91210</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>491334</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6943239</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>126528453</v>
+      </c>
+      <c r="B172" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>491196</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6943333</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>126528443</v>
+      </c>
+      <c r="B173" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>491208</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6943293</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF173" t="inlineStr"/>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>126522903</v>
+      </c>
+      <c r="B174" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>StorÖravattnet, StorÖravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>491331</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6943394</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>126528447</v>
+      </c>
+      <c r="B175" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>491348</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6943314</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>126528437</v>
+      </c>
+      <c r="B176" t="n">
+        <v>96614</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>53</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>491236</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6943308</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>126523340</v>
+      </c>
+      <c r="B177" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>491361</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6943309</v>
+      </c>
+      <c r="S177" t="n">
+        <v>10</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>126528441</v>
+      </c>
+      <c r="B178" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>491350</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6943275</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>126528451</v>
+      </c>
+      <c r="B179" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>491335</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6943226</v>
+      </c>
+      <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>126528445</v>
+      </c>
+      <c r="B180" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>491202</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6943300</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>126528450</v>
+      </c>
+      <c r="B181" t="n">
+        <v>105396</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>491225</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6943291</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>126528452</v>
+      </c>
+      <c r="B182" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>491184</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6943353</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>126528449</v>
+      </c>
+      <c r="B183" t="n">
+        <v>105396</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>491202</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6943313</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>126528444</v>
+      </c>
+      <c r="B184" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>491191</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6943335</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>126528438</v>
+      </c>
+      <c r="B185" t="n">
+        <v>96614</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>53</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>491202</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6943328</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>126528440</v>
+      </c>
+      <c r="B186" t="n">
+        <v>91210</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>491241</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6943299</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>126523315</v>
+      </c>
+      <c r="B187" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>491361</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6943309</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>126528446</v>
+      </c>
+      <c r="B188" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>491357</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6943287</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>126528442</v>
+      </c>
+      <c r="B189" t="n">
+        <v>79569</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>491341</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6943272</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>126528436</v>
+      </c>
+      <c r="B190" t="n">
+        <v>96614</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>53</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>491294</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6943344</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>126528435</v>
+      </c>
+      <c r="B191" t="n">
+        <v>96614</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>53</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>491337</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6943377</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -19468,7 +19468,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126523129</v>
+        <v>126528453</v>
       </c>
       <c r="B170" t="n">
         <v>78980</v>
@@ -19499,14 +19499,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>491352</v>
+        <v>491196</v>
       </c>
       <c r="R170" t="n">
-        <v>6943338</v>
+        <v>6943333</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19536,19 +19536,9 @@
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>19:25</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>19:25</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19563,57 +19553,57 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126528439</v>
+        <v>126523129</v>
       </c>
       <c r="B171" t="n">
-        <v>91210</v>
+        <v>78980</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>491334</v>
+        <v>491352</v>
       </c>
       <c r="R171" t="n">
-        <v>6943239</v>
+        <v>6943338</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19643,9 +19633,19 @@
           <t>2025-07-08</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19660,44 +19660,44 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126528453</v>
+        <v>126528439</v>
       </c>
       <c r="B172" t="n">
-        <v>78980</v>
+        <v>91210</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19707,10 +19707,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>491196</v>
+        <v>491334</v>
       </c>
       <c r="R172" t="n">
-        <v>6943333</v>
+        <v>6943239</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19879,7 +19879,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126522903</v>
+        <v>126528447</v>
       </c>
       <c r="B174" t="n">
         <v>98361</v>
@@ -19909,19 +19909,27 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>StorÖravattnet, StorÖravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>491331</v>
+        <v>491348</v>
       </c>
       <c r="R174" t="n">
-        <v>6943394</v>
+        <v>6943314</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19951,46 +19959,37 @@
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126528447</v>
+        <v>126522903</v>
       </c>
       <c r="B175" t="n">
         <v>98361</v>
@@ -20020,27 +20019,19 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>StorÖravattnet, StorÖravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>491348</v>
+        <v>491331</v>
       </c>
       <c r="R175" t="n">
-        <v>6943314</v>
+        <v>6943394</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20070,30 +20061,39 @@
           <t>2025-07-08</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-07-08</t>
         </is>
       </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -20903,57 +20903,45 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>126528444</v>
+        <v>126528438</v>
       </c>
       <c r="B184" t="n">
-        <v>98361</v>
+        <v>96614</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>491191</v>
+        <v>491202</v>
       </c>
       <c r="R184" t="n">
-        <v>6943335</v>
+        <v>6943328</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20994,7 +20982,6 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -21013,45 +21000,57 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126528438</v>
+        <v>126528444</v>
       </c>
       <c r="B185" t="n">
-        <v>96614</v>
+        <v>98361</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>491202</v>
+        <v>491191</v>
       </c>
       <c r="R185" t="n">
-        <v>6943328</v>
+        <v>6943335</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21092,6 +21091,7 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -21207,45 +21207,57 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>126523315</v>
+        <v>126528446</v>
       </c>
       <c r="B187" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>491361</v>
+        <v>491357</v>
       </c>
       <c r="R187" t="n">
-        <v>6943309</v>
+        <v>6943287</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21275,96 +21287,75 @@
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>19:32</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>19:32</t>
-        </is>
-      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126528446</v>
+        <v>126523315</v>
       </c>
       <c r="B188" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>491357</v>
+        <v>491361</v>
       </c>
       <c r="R188" t="n">
-        <v>6943287</v>
+        <v>6943309</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21394,40 +21385,49 @@
           <t>2025-07-08</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-07-08</t>
         </is>
       </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126528442</v>
+        <v>126528436</v>
       </c>
       <c r="B189" t="n">
-        <v>79569</v>
+        <v>96614</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21435,21 +21435,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21459,10 +21459,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>491341</v>
+        <v>491294</v>
       </c>
       <c r="R189" t="n">
-        <v>6943272</v>
+        <v>6943344</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21521,10 +21521,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126528436</v>
+        <v>126528442</v>
       </c>
       <c r="B190" t="n">
-        <v>96614</v>
+        <v>79569</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21532,21 +21532,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21556,10 +21556,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>491294</v>
+        <v>491341</v>
       </c>
       <c r="R190" t="n">
-        <v>6943344</v>
+        <v>6943272</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21000,57 +21000,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126528444</v>
+        <v>126528440</v>
       </c>
       <c r="B185" t="n">
-        <v>98361</v>
+        <v>91210</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>491191</v>
+        <v>491241</v>
       </c>
       <c r="R185" t="n">
-        <v>6943335</v>
+        <v>6943299</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21091,7 +21079,6 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -21110,45 +21097,57 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>126528440</v>
+        <v>126528444</v>
       </c>
       <c r="B186" t="n">
-        <v>91210</v>
+        <v>98361</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>491241</v>
+        <v>491191</v>
       </c>
       <c r="R186" t="n">
-        <v>6943299</v>
+        <v>6943335</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21189,6 +21188,7 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21000,45 +21000,57 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126528440</v>
+        <v>126528444</v>
       </c>
       <c r="B185" t="n">
-        <v>91210</v>
+        <v>98361</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>491241</v>
+        <v>491191</v>
       </c>
       <c r="R185" t="n">
-        <v>6943299</v>
+        <v>6943335</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21079,6 +21091,7 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -21097,57 +21110,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>126528444</v>
+        <v>126528440</v>
       </c>
       <c r="B186" t="n">
-        <v>98361</v>
+        <v>91210</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>491191</v>
+        <v>491241</v>
       </c>
       <c r="R186" t="n">
-        <v>6943335</v>
+        <v>6943299</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21188,7 +21189,6 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
-      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21207,57 +21207,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>126528446</v>
+        <v>126523315</v>
       </c>
       <c r="B187" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>491357</v>
+        <v>491361</v>
       </c>
       <c r="R187" t="n">
-        <v>6943287</v>
+        <v>6943309</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21287,75 +21275,96 @@
           <t>2025-07-08</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-07-08</t>
         </is>
       </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126523315</v>
+        <v>126528446</v>
       </c>
       <c r="B188" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>491361</v>
+        <v>491357</v>
       </c>
       <c r="R188" t="n">
-        <v>6943309</v>
+        <v>6943287</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21385,39 +21394,30 @@
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>19:32</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>19:32</t>
-        </is>
-      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
       <c r="AE188" t="b">
         <v>0</v>
       </c>
+      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21718,7 +21718,7 @@
         <v>126917369</v>
       </c>
       <c r="B192" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>126918107</v>
       </c>
       <c r="B193" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>126918547</v>
       </c>
       <c r="B194" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>126918192</v>
       </c>
       <c r="B196" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>126917926</v>
       </c>
       <c r="B197" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>126917580</v>
       </c>
       <c r="B198" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>126918474</v>
       </c>
       <c r="B199" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>126918541</v>
       </c>
       <c r="B200" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>126917422</v>
       </c>
       <c r="B201" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>126918483</v>
       </c>
       <c r="B202" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>126918130</v>
       </c>
       <c r="B203" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21718,7 +21718,7 @@
         <v>126917369</v>
       </c>
       <c r="B192" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>126918107</v>
       </c>
       <c r="B193" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21929,45 +21929,59 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126918547</v>
+        <v>126918262</v>
       </c>
       <c r="B194" t="n">
-        <v>78678</v>
+        <v>56849</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>490878</v>
+        <v>490893</v>
       </c>
       <c r="R194" t="n">
-        <v>6943827</v>
+        <v>6943868</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21999,7 +22013,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22009,7 +22023,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22036,59 +22050,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126918262</v>
+        <v>126918547</v>
       </c>
       <c r="B195" t="n">
-        <v>56849</v>
+        <v>78681</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>490893</v>
+        <v>490878</v>
       </c>
       <c r="R195" t="n">
-        <v>6943868</v>
+        <v>6943827</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22160,7 +22160,7 @@
         <v>126918192</v>
       </c>
       <c r="B196" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>126917926</v>
       </c>
       <c r="B197" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>126917580</v>
       </c>
       <c r="B198" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>126918474</v>
       </c>
       <c r="B199" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>126918541</v>
       </c>
       <c r="B200" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>126917422</v>
       </c>
       <c r="B201" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>126918483</v>
       </c>
       <c r="B202" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>126918130</v>
       </c>
       <c r="B203" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21929,59 +21929,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126918262</v>
+        <v>126918547</v>
       </c>
       <c r="B194" t="n">
-        <v>56849</v>
+        <v>78681</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>490893</v>
+        <v>490878</v>
       </c>
       <c r="R194" t="n">
-        <v>6943868</v>
+        <v>6943827</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22013,7 +21999,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22023,7 +22009,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22050,45 +22036,59 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126918547</v>
+        <v>126918262</v>
       </c>
       <c r="B195" t="n">
-        <v>78681</v>
+        <v>56849</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>490878</v>
+        <v>490893</v>
       </c>
       <c r="R195" t="n">
-        <v>6943827</v>
+        <v>6943868</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD195" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21929,45 +21929,59 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126918547</v>
+        <v>126918262</v>
       </c>
       <c r="B194" t="n">
-        <v>78681</v>
+        <v>56849</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>490878</v>
+        <v>490893</v>
       </c>
       <c r="R194" t="n">
-        <v>6943827</v>
+        <v>6943868</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21999,7 +22013,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22009,7 +22023,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22036,59 +22050,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126918262</v>
+        <v>126918547</v>
       </c>
       <c r="B195" t="n">
-        <v>56849</v>
+        <v>78681</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>490893</v>
+        <v>490878</v>
       </c>
       <c r="R195" t="n">
-        <v>6943868</v>
+        <v>6943827</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD195" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21718,7 +21718,7 @@
         <v>126917369</v>
       </c>
       <c r="B192" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>126918107</v>
       </c>
       <c r="B193" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21929,59 +21929,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126918262</v>
+        <v>126918547</v>
       </c>
       <c r="B194" t="n">
-        <v>56849</v>
+        <v>78685</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>490893</v>
+        <v>490878</v>
       </c>
       <c r="R194" t="n">
-        <v>6943868</v>
+        <v>6943827</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22013,7 +21999,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22023,7 +22009,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22050,45 +22036,59 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126918547</v>
+        <v>126918262</v>
       </c>
       <c r="B195" t="n">
-        <v>78681</v>
+        <v>56853</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>490878</v>
+        <v>490893</v>
       </c>
       <c r="R195" t="n">
-        <v>6943827</v>
+        <v>6943868</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22160,7 +22160,7 @@
         <v>126918192</v>
       </c>
       <c r="B196" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>126917926</v>
       </c>
       <c r="B197" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>126917580</v>
       </c>
       <c r="B198" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>126918474</v>
       </c>
       <c r="B199" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>126918541</v>
       </c>
       <c r="B200" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>126917422</v>
       </c>
       <c r="B201" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>126918483</v>
       </c>
       <c r="B202" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>126918130</v>
       </c>
       <c r="B203" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -22478,7 +22478,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126918474</v>
+        <v>126918541</v>
       </c>
       <c r="B199" t="n">
         <v>79636</v>
@@ -22513,10 +22513,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>490897</v>
+        <v>490878</v>
       </c>
       <c r="R199" t="n">
-        <v>6943855</v>
+        <v>6943827</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22548,7 +22548,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22558,7 +22558,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22585,7 +22585,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126918541</v>
+        <v>126918474</v>
       </c>
       <c r="B200" t="n">
         <v>79636</v>
@@ -22620,10 +22620,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>490878</v>
+        <v>490897</v>
       </c>
       <c r="R200" t="n">
-        <v>6943827</v>
+        <v>6943855</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22655,7 +22655,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AD200" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21929,45 +21929,59 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126918547</v>
+        <v>126918262</v>
       </c>
       <c r="B194" t="n">
-        <v>78685</v>
+        <v>56853</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>490878</v>
+        <v>490893</v>
       </c>
       <c r="R194" t="n">
-        <v>6943827</v>
+        <v>6943868</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21999,7 +22013,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22009,7 +22023,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22036,59 +22050,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126918262</v>
+        <v>126918547</v>
       </c>
       <c r="B195" t="n">
-        <v>56853</v>
+        <v>78685</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>490893</v>
+        <v>490878</v>
       </c>
       <c r="R195" t="n">
-        <v>6943868</v>
+        <v>6943827</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD195" t="b">

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21718,7 +21718,7 @@
         <v>126917369</v>
       </c>
       <c r="B192" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>126918107</v>
       </c>
       <c r="B193" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21929,59 +21929,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126918262</v>
+        <v>126918547</v>
       </c>
       <c r="B194" t="n">
-        <v>56853</v>
+        <v>78687</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>490893</v>
+        <v>490878</v>
       </c>
       <c r="R194" t="n">
-        <v>6943868</v>
+        <v>6943827</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22013,7 +21999,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22023,7 +22009,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22050,45 +22036,59 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126918547</v>
+        <v>126918262</v>
       </c>
       <c r="B195" t="n">
-        <v>78685</v>
+        <v>56855</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>490878</v>
+        <v>490893</v>
       </c>
       <c r="R195" t="n">
-        <v>6943827</v>
+        <v>6943868</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22160,7 +22160,7 @@
         <v>126918192</v>
       </c>
       <c r="B196" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>126917926</v>
       </c>
       <c r="B197" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>126917580</v>
       </c>
       <c r="B198" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22478,10 +22478,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126918541</v>
+        <v>126918474</v>
       </c>
       <c r="B199" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22513,10 +22513,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>490878</v>
+        <v>490897</v>
       </c>
       <c r="R199" t="n">
-        <v>6943827</v>
+        <v>6943855</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22548,7 +22548,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22558,7 +22558,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22585,10 +22585,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126918474</v>
+        <v>126918541</v>
       </c>
       <c r="B200" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22620,10 +22620,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>490897</v>
+        <v>490878</v>
       </c>
       <c r="R200" t="n">
-        <v>6943855</v>
+        <v>6943827</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22655,7 +22655,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22695,7 +22695,7 @@
         <v>126917422</v>
       </c>
       <c r="B201" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>126918483</v>
       </c>
       <c r="B202" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>126918130</v>
       </c>
       <c r="B203" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY203"/>
+  <dimension ref="A1:AY204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23011,6 +23011,115 @@
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>128697601</v>
+      </c>
+      <c r="B204" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Salomsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>491117</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6943534</v>
+      </c>
+      <c r="S204" t="n">
+        <v>25</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY204"/>
+  <dimension ref="A1:AY206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23120,6 +23120,224 @@
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>128742608</v>
+      </c>
+      <c r="B205" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Salomsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>491239</v>
+      </c>
+      <c r="R205" t="n">
+        <v>6943492</v>
+      </c>
+      <c r="S205" t="n">
+        <v>25</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>128742195</v>
+      </c>
+      <c r="B206" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Salomsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>490961</v>
+      </c>
+      <c r="R206" t="n">
+        <v>6943659</v>
+      </c>
+      <c r="S206" t="n">
+        <v>25</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -23016,7 +23016,7 @@
         <v>128697601</v>
       </c>
       <c r="B204" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>128742608</v>
       </c>
       <c r="B205" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>128742195</v>
       </c>
       <c r="B206" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -23016,7 +23016,7 @@
         <v>128697601</v>
       </c>
       <c r="B204" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>128742608</v>
       </c>
       <c r="B205" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>128742195</v>
       </c>
       <c r="B206" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -23016,7 +23016,7 @@
         <v>128697601</v>
       </c>
       <c r="B204" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>128742608</v>
       </c>
       <c r="B205" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>128742195</v>
       </c>
       <c r="B206" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -23016,7 +23016,7 @@
         <v>128697601</v>
       </c>
       <c r="B204" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>128742608</v>
       </c>
       <c r="B205" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>128742195</v>
       </c>
       <c r="B206" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -23125,7 +23125,7 @@
         <v>128742608</v>
       </c>
       <c r="B205" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>128742195</v>
       </c>
       <c r="B206" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -21718,7 +21718,7 @@
         <v>126917369</v>
       </c>
       <c r="B192" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>126918107</v>
       </c>
       <c r="B193" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>126918547</v>
       </c>
       <c r="B194" t="n">
-        <v>78687</v>
+        <v>78678</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>126918262</v>
       </c>
       <c r="B195" t="n">
-        <v>56855</v>
+        <v>56849</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>126918192</v>
       </c>
       <c r="B196" t="n">
-        <v>80151</v>
+        <v>80142</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>126917926</v>
       </c>
       <c r="B197" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>126917580</v>
       </c>
       <c r="B198" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>126918474</v>
       </c>
       <c r="B199" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>126918541</v>
       </c>
       <c r="B200" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>126917422</v>
       </c>
       <c r="B201" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>126918483</v>
       </c>
       <c r="B202" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>126918130</v>
       </c>
       <c r="B203" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>

--- a/artfynd/A 47127-2024 artfynd.xlsx
+++ b/artfynd/A 47127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY207"/>
+  <dimension ref="A1:AZ207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528435</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528436</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528437</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528438</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125771144</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807677</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121542897</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125748931</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125753755</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807673</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1773,6 +1828,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918547</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1870,6 +1930,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807676</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120719729</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2084,6 +2154,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121541418</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121541688</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,6 +2378,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121722647</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2395,6 +2480,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125771024</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2502,6 +2592,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121541432</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747107</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2716,6 +2816,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718636</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2823,6 +2928,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120719097</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2930,6 +3040,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747725</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3027,6 +3142,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807672</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3124,6 +3244,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807674</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3221,6 +3346,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528439</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3318,6 +3448,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528440</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3425,6 +3560,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119560369</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3532,6 +3672,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120716605</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3639,6 +3784,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120717201</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3751,6 +3901,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718874</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3863,6 +4018,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722670</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3970,6 +4130,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120742766</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4075,6 +4240,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120774951</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4182,6 +4352,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121540892</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4289,6 +4464,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121540990</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4396,6 +4576,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121541195</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4503,6 +4688,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121541348</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4610,6 +4800,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121541599</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4717,6 +4912,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121542322</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4824,6 +5024,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121542839</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4931,6 +5136,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126522996</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5038,6 +5248,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126523129</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5145,6 +5360,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126523315</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5242,6 +5462,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528451</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5339,6 +5564,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528452</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5436,6 +5666,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528453</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5543,6 +5778,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917369</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5650,6 +5890,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918107</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5747,6 +5992,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807669</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5854,6 +6104,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747830</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5966,6 +6221,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125748705</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6073,6 +6333,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125769296</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6180,6 +6445,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125749113</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6277,6 +6547,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125770538</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6374,6 +6649,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528441</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6481,6 +6761,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917422</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6588,6 +6873,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917926</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6695,6 +6985,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918474</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6802,6 +7097,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918541</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6909,6 +7209,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120716811</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7016,6 +7321,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120716895</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7123,6 +7433,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120716923</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7230,6 +7545,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120716975</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7337,6 +7657,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120717222</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7444,6 +7769,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120717815</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7556,6 +7886,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718119</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7663,6 +7998,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718129</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7770,6 +8110,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718184</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7877,6 +8222,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718425</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7989,6 +8339,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718503</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8096,6 +8451,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718792</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8203,6 +8563,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120719261</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8310,6 +8675,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120719928</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8417,6 +8787,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721572</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8524,6 +8899,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722277</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8631,6 +9011,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722355</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8738,6 +9123,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722491</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8845,6 +9235,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722705</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8952,6 +9347,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722809</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9059,6 +9459,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722927</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9166,6 +9571,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120723664</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9273,6 +9683,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120723859</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9380,6 +9795,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120742530</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9487,6 +9907,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120743110</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9594,6 +10019,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120743239</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9699,6 +10129,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120774807</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9808,6 +10243,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120777334</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9917,6 +10357,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120777688</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10023,6 +10468,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121172997</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10124,6 +10574,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173022</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10225,6 +10680,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173030</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10326,6 +10786,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173037</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10427,6 +10892,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173054</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10528,6 +10998,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173058</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10629,6 +11104,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173066</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10730,6 +11210,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173075</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10831,6 +11316,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173088</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10932,6 +11422,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174670</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11039,6 +11534,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121540656</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11146,6 +11646,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121541493</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11253,6 +11758,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121722526</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11350,6 +11860,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807675</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11447,6 +11962,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807678</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11554,6 +12074,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917580</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11661,6 +12186,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918130</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11768,6 +12298,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747204</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11875,6 +12410,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918192</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11982,6 +12522,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747114</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12089,6 +12634,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125748742</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12201,6 +12751,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718757</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12313,6 +12868,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120719137</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12425,6 +12985,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120723068</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12534,6 +13099,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742608</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12643,6 +13213,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173006</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12755,6 +13330,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121542288</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12877,6 +13457,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121542668</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12979,6 +13564,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807671</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13100,6 +13690,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918262</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13212,6 +13807,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718395</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13321,6 +13921,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128697601</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13430,6 +14035,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742195</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13532,6 +14142,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121659358</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13634,6 +14249,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121659363</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13750,6 +14370,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120716606</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13866,6 +14491,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120716666</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13982,6 +14612,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718824</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14093,6 +14728,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718862</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14209,6 +14849,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718989</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14325,6 +14970,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120719003</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14441,6 +15091,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120719150</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14557,6 +15212,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120719217</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14673,6 +15333,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120719275</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14789,6 +15454,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721536</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14896,6 +15566,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721736</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15012,6 +15687,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722329</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15128,6 +15808,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722730</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15244,6 +15929,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722814</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15360,6 +16050,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722993</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15470,6 +16165,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120774658</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15580,6 +16280,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120774880</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15690,6 +16395,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120774962</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15800,6 +16510,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120774995</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15910,6 +16625,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120777458</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16020,6 +16740,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120777695</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16130,6 +16855,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120777709</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16240,6 +16970,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120777722</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16350,6 +17085,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120777732</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16460,6 +17200,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120778013</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16566,6 +17311,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120778019</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16676,6 +17426,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120778039</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16782,6 +17537,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120778050</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16892,6 +17652,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120778061</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17002,6 +17767,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120778125</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17112,6 +17882,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120778153</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17222,6 +17997,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120778167</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17332,6 +18112,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120846304</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17442,6 +18227,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120846313</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17552,6 +18342,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173042</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17662,6 +18457,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173047</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17772,6 +18572,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173101</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17882,6 +18687,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173118</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17992,6 +18802,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174608</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18102,6 +18917,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174619</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18212,6 +19032,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174638</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18322,6 +19147,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174642</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18432,6 +19262,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174644</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18542,6 +19377,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174651</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18652,6 +19492,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174660</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18762,6 +19607,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174681</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18872,6 +19722,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174691</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18982,6 +19837,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174703</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19092,6 +19952,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174710</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19202,6 +20067,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174716</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19312,6 +20182,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174736</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19422,6 +20297,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121174973</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19532,6 +20412,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121175096</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19638,6 +20523,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121175104</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19745,6 +20635,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125748199</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19856,6 +20751,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126521894</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19967,6 +20867,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126522903</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20078,6 +20983,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126523340</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20188,6 +21098,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528443</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20298,6 +21213,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528444</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20408,6 +21328,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528445</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20518,6 +21443,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528446</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20628,6 +21558,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528447</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20725,6 +21660,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528449</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20822,6 +21762,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528450</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20929,6 +21874,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120723431</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21039,6 +21989,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120774989</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21146,6 +22101,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120717812</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21253,6 +22213,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722853</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21369,6 +22334,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120723037</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21476,6 +22446,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120742687</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21578,6 +22553,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120846326</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21685,6 +22665,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120723495</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21792,6 +22777,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121541303</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21899,6 +22889,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121543021</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22006,6 +23001,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125748749</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22117,6 +23117,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125770743</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22224,6 +23229,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918483</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22331,6 +23341,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121540625</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22443,6 +23458,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121540870</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22550,6 +23570,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121541329</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22647,6 +23672,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807670</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22744,8 +23774,221 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528442</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>